--- a/tigo_import_500_empleados_nuevos_datos.xlsx
+++ b/tigo_import_500_empleados_nuevos_datos.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6AA8D560-AC4F-42D6-913B-B67029237B06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Santiago Roman\OneDrive\Escritorio\giftApp\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AA6537A-2DC9-4ED3-BC7F-900C047B1844}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Importacion" sheetId="1" r:id="rId1"/>
@@ -186,7 +191,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8226" uniqueCount="3464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8226" uniqueCount="3465">
   <si>
     <t>campaignSlug</t>
   </si>
@@ -10578,13 +10583,16 @@
   </si>
   <si>
     <t>Nota: algunos empleados tienen hasta 6 beneficiarios para probar importaciones con múltiples hijos.</t>
+  </si>
+  <si>
+    <t>tigo-20261</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -10962,7 +10970,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J911"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -10976,7 +10984,7 @@
     <col min="10" max="10" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -11008,9 +11016,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>10</v>
+        <v>3464</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>11</v>
@@ -11040,7 +11048,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -11072,7 +11080,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -11104,7 +11112,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -11136,7 +11144,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -11168,7 +11176,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -11200,7 +11208,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -11232,7 +11240,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>10</v>
       </c>
@@ -11264,7 +11272,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
@@ -11296,7 +11304,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -11328,7 +11336,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
@@ -11360,7 +11368,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>10</v>
       </c>
@@ -11392,7 +11400,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>10</v>
       </c>
@@ -11424,7 +11432,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>10</v>
       </c>
@@ -11456,7 +11464,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>10</v>
       </c>
@@ -11488,7 +11496,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>10</v>
       </c>
@@ -11520,7 +11528,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>10</v>
       </c>
@@ -11552,7 +11560,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>10</v>
       </c>
@@ -11584,7 +11592,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>10</v>
       </c>
@@ -11616,7 +11624,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>10</v>
       </c>
@@ -11648,7 +11656,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>10</v>
       </c>
@@ -11680,7 +11688,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>10</v>
       </c>
@@ -11712,7 +11720,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>10</v>
       </c>
@@ -11744,7 +11752,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>10</v>
       </c>
@@ -11776,7 +11784,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>10</v>
       </c>
@@ -11808,7 +11816,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>10</v>
       </c>
@@ -11840,7 +11848,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>10</v>
       </c>
@@ -11872,7 +11880,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>10</v>
       </c>
@@ -11904,7 +11912,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>10</v>
       </c>
@@ -11936,7 +11944,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>10</v>
       </c>
@@ -11968,7 +11976,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>10</v>
       </c>
@@ -12000,7 +12008,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>10</v>
       </c>
@@ -12032,7 +12040,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>10</v>
       </c>
@@ -12064,7 +12072,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>10</v>
       </c>
@@ -12096,7 +12104,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>10</v>
       </c>
@@ -12128,7 +12136,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>10</v>
       </c>
@@ -12160,7 +12168,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>10</v>
       </c>
@@ -12192,7 +12200,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>10</v>
       </c>
@@ -12224,7 +12232,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="40" spans="1:10">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>10</v>
       </c>
@@ -12256,7 +12264,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:10">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>10</v>
       </c>
@@ -12288,7 +12296,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:10">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>10</v>
       </c>
@@ -12320,7 +12328,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="43" spans="1:10">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>10</v>
       </c>
@@ -12352,7 +12360,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="44" spans="1:10">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>10</v>
       </c>
@@ -12384,7 +12392,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:10">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>10</v>
       </c>
@@ -12416,7 +12424,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:10">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>10</v>
       </c>
@@ -12448,7 +12456,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="47" spans="1:10">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>10</v>
       </c>
@@ -12480,7 +12488,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="48" spans="1:10">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>10</v>
       </c>
@@ -12512,7 +12520,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49" spans="1:10">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>10</v>
       </c>
@@ -12544,7 +12552,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="50" spans="1:10">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>10</v>
       </c>
@@ -12576,7 +12584,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="51" spans="1:10">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>10</v>
       </c>
@@ -12608,7 +12616,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="52" spans="1:10">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>10</v>
       </c>
@@ -12640,7 +12648,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="53" spans="1:10">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>10</v>
       </c>
@@ -12672,7 +12680,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="54" spans="1:10">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>10</v>
       </c>
@@ -12704,7 +12712,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="55" spans="1:10">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>10</v>
       </c>
@@ -12736,7 +12744,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="56" spans="1:10">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>10</v>
       </c>
@@ -12768,7 +12776,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="57" spans="1:10">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>10</v>
       </c>
@@ -12800,7 +12808,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="58" spans="1:10">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>10</v>
       </c>
@@ -12832,7 +12840,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="59" spans="1:10">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>10</v>
       </c>
@@ -12864,7 +12872,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="60" spans="1:10">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>10</v>
       </c>
@@ -12896,7 +12904,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="61" spans="1:10">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>10</v>
       </c>
@@ -12928,7 +12936,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="62" spans="1:10">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>10</v>
       </c>
@@ -12960,7 +12968,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="63" spans="1:10">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>10</v>
       </c>
@@ -12992,7 +13000,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="64" spans="1:10">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>10</v>
       </c>
@@ -13024,7 +13032,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="65" spans="1:10">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>10</v>
       </c>
@@ -13056,7 +13064,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="66" spans="1:10">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>10</v>
       </c>
@@ -13088,7 +13096,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="67" spans="1:10">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>10</v>
       </c>
@@ -13120,7 +13128,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="68" spans="1:10">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>10</v>
       </c>
@@ -13152,7 +13160,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="69" spans="1:10">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>10</v>
       </c>
@@ -13184,7 +13192,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="70" spans="1:10">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>10</v>
       </c>
@@ -13216,7 +13224,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="71" spans="1:10">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>10</v>
       </c>
@@ -13248,7 +13256,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="72" spans="1:10">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>10</v>
       </c>
@@ -13280,7 +13288,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="73" spans="1:10">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>10</v>
       </c>
@@ -13312,7 +13320,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="74" spans="1:10">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>10</v>
       </c>
@@ -13344,7 +13352,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="75" spans="1:10">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>10</v>
       </c>
@@ -13376,7 +13384,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="76" spans="1:10">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>10</v>
       </c>
@@ -13408,7 +13416,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="77" spans="1:10">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>10</v>
       </c>
@@ -13440,7 +13448,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="78" spans="1:10">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>10</v>
       </c>
@@ -13472,7 +13480,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="79" spans="1:10">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>10</v>
       </c>
@@ -13504,7 +13512,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="80" spans="1:10">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>10</v>
       </c>
@@ -13536,7 +13544,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="81" spans="1:10">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>10</v>
       </c>
@@ -13568,7 +13576,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="82" spans="1:10">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>10</v>
       </c>
@@ -13600,7 +13608,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="83" spans="1:10">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>10</v>
       </c>
@@ -13632,7 +13640,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="84" spans="1:10">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>10</v>
       </c>
@@ -13664,7 +13672,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="85" spans="1:10">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>10</v>
       </c>
@@ -13696,7 +13704,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="86" spans="1:10">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>10</v>
       </c>
@@ -13728,7 +13736,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="87" spans="1:10">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
         <v>10</v>
       </c>
@@ -13760,7 +13768,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="88" spans="1:10">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>10</v>
       </c>
@@ -13792,7 +13800,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="89" spans="1:10">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
         <v>10</v>
       </c>
@@ -13824,7 +13832,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="90" spans="1:10">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>10</v>
       </c>
@@ -13856,7 +13864,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="91" spans="1:10">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>10</v>
       </c>
@@ -13888,7 +13896,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="92" spans="1:10">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
         <v>10</v>
       </c>
@@ -13920,7 +13928,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="93" spans="1:10">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>10</v>
       </c>
@@ -13952,7 +13960,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="94" spans="1:10">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
         <v>10</v>
       </c>
@@ -13984,7 +13992,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="95" spans="1:10">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
         <v>10</v>
       </c>
@@ -14016,7 +14024,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="96" spans="1:10">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
         <v>10</v>
       </c>
@@ -14048,7 +14056,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="97" spans="1:10">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
         <v>10</v>
       </c>
@@ -14080,7 +14088,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="98" spans="1:10">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
         <v>10</v>
       </c>
@@ -14112,7 +14120,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="99" spans="1:10">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
         <v>10</v>
       </c>
@@ -14144,7 +14152,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="100" spans="1:10">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
         <v>10</v>
       </c>
@@ -14176,7 +14184,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="101" spans="1:10">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
         <v>10</v>
       </c>
@@ -14208,7 +14216,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="102" spans="1:10">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
         <v>10</v>
       </c>
@@ -14240,7 +14248,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="103" spans="1:10">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
         <v>10</v>
       </c>
@@ -14272,7 +14280,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="104" spans="1:10">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
         <v>10</v>
       </c>
@@ -14304,7 +14312,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="105" spans="1:10">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
         <v>10</v>
       </c>
@@ -14336,7 +14344,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="106" spans="1:10">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
         <v>10</v>
       </c>
@@ -14368,7 +14376,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="107" spans="1:10">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
         <v>10</v>
       </c>
@@ -14400,7 +14408,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="108" spans="1:10">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
         <v>10</v>
       </c>
@@ -14432,7 +14440,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="109" spans="1:10">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
         <v>10</v>
       </c>
@@ -14464,7 +14472,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="110" spans="1:10">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
         <v>10</v>
       </c>
@@ -14496,7 +14504,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="111" spans="1:10">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
         <v>10</v>
       </c>
@@ -14528,7 +14536,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="112" spans="1:10">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
         <v>10</v>
       </c>
@@ -14560,7 +14568,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="113" spans="1:10">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
         <v>10</v>
       </c>
@@ -14592,7 +14600,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="114" spans="1:10">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
         <v>10</v>
       </c>
@@ -14624,7 +14632,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="115" spans="1:10">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
         <v>10</v>
       </c>
@@ -14656,7 +14664,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="116" spans="1:10">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
         <v>10</v>
       </c>
@@ -14688,7 +14696,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="117" spans="1:10">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
         <v>10</v>
       </c>
@@ -14720,7 +14728,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="118" spans="1:10">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
         <v>10</v>
       </c>
@@ -14752,7 +14760,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="119" spans="1:10">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
         <v>10</v>
       </c>
@@ -14784,7 +14792,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="120" spans="1:10">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
         <v>10</v>
       </c>
@@ -14816,7 +14824,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="121" spans="1:10">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
         <v>10</v>
       </c>
@@ -14848,7 +14856,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="122" spans="1:10">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
         <v>10</v>
       </c>
@@ -14880,7 +14888,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="123" spans="1:10">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
         <v>10</v>
       </c>
@@ -14912,7 +14920,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="124" spans="1:10">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
         <v>10</v>
       </c>
@@ -14944,7 +14952,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="125" spans="1:10">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
         <v>10</v>
       </c>
@@ -14976,7 +14984,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="126" spans="1:10">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
         <v>10</v>
       </c>
@@ -15008,7 +15016,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="127" spans="1:10">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
         <v>10</v>
       </c>
@@ -15040,7 +15048,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="128" spans="1:10">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
         <v>10</v>
       </c>
@@ -15072,7 +15080,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="129" spans="1:10">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
         <v>10</v>
       </c>
@@ -15104,7 +15112,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="130" spans="1:10">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
         <v>10</v>
       </c>
@@ -15136,7 +15144,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="131" spans="1:10">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
         <v>10</v>
       </c>
@@ -15168,7 +15176,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="132" spans="1:10">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
         <v>10</v>
       </c>
@@ -15200,7 +15208,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="133" spans="1:10">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
         <v>10</v>
       </c>
@@ -15232,7 +15240,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="134" spans="1:10">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
         <v>10</v>
       </c>
@@ -15264,7 +15272,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="135" spans="1:10">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
         <v>10</v>
       </c>
@@ -15296,7 +15304,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="136" spans="1:10">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
         <v>10</v>
       </c>
@@ -15328,7 +15336,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="137" spans="1:10">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
         <v>10</v>
       </c>
@@ -15360,7 +15368,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="138" spans="1:10">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
         <v>10</v>
       </c>
@@ -15392,7 +15400,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="139" spans="1:10">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
         <v>10</v>
       </c>
@@ -15424,7 +15432,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="140" spans="1:10">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
         <v>10</v>
       </c>
@@ -15456,7 +15464,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="141" spans="1:10">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
         <v>10</v>
       </c>
@@ -15488,7 +15496,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="142" spans="1:10">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
         <v>10</v>
       </c>
@@ -15520,7 +15528,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="143" spans="1:10">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
         <v>10</v>
       </c>
@@ -15552,7 +15560,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="144" spans="1:10">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
         <v>10</v>
       </c>
@@ -15584,7 +15592,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="145" spans="1:10">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
         <v>10</v>
       </c>
@@ -15616,7 +15624,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="146" spans="1:10">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
         <v>10</v>
       </c>
@@ -15648,7 +15656,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="147" spans="1:10">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
         <v>10</v>
       </c>
@@ -15680,7 +15688,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="148" spans="1:10">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
         <v>10</v>
       </c>
@@ -15712,7 +15720,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="149" spans="1:10">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
         <v>10</v>
       </c>
@@ -15744,7 +15752,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="150" spans="1:10">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
         <v>10</v>
       </c>
@@ -15776,7 +15784,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="151" spans="1:10">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
         <v>10</v>
       </c>
@@ -15808,7 +15816,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="152" spans="1:10">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
         <v>10</v>
       </c>
@@ -15840,7 +15848,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="153" spans="1:10">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
         <v>10</v>
       </c>
@@ -15872,7 +15880,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="154" spans="1:10">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
         <v>10</v>
       </c>
@@ -15904,7 +15912,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="155" spans="1:10">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
         <v>10</v>
       </c>
@@ -15936,7 +15944,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="156" spans="1:10">
+    <row r="156" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
         <v>10</v>
       </c>
@@ -15968,7 +15976,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="157" spans="1:10">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
         <v>10</v>
       </c>
@@ -16000,7 +16008,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="158" spans="1:10">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
         <v>10</v>
       </c>
@@ -16032,7 +16040,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="159" spans="1:10">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="s">
         <v>10</v>
       </c>
@@ -16064,7 +16072,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="160" spans="1:10">
+    <row r="160" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
         <v>10</v>
       </c>
@@ -16096,7 +16104,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="161" spans="1:10">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
         <v>10</v>
       </c>
@@ -16128,7 +16136,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="162" spans="1:10">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
         <v>10</v>
       </c>
@@ -16160,7 +16168,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="163" spans="1:10">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
         <v>10</v>
       </c>
@@ -16192,7 +16200,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="164" spans="1:10">
+    <row r="164" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
         <v>10</v>
       </c>
@@ -16224,7 +16232,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="165" spans="1:10">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="s">
         <v>10</v>
       </c>
@@ -16256,7 +16264,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="166" spans="1:10">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
         <v>10</v>
       </c>
@@ -16288,7 +16296,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="167" spans="1:10">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="s">
         <v>10</v>
       </c>
@@ -16320,7 +16328,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="168" spans="1:10">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
         <v>10</v>
       </c>
@@ -16352,7 +16360,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="169" spans="1:10">
+    <row r="169" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A169" s="2" t="s">
         <v>10</v>
       </c>
@@ -16384,7 +16392,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="170" spans="1:10">
+    <row r="170" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
         <v>10</v>
       </c>
@@ -16416,7 +16424,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="171" spans="1:10">
+    <row r="171" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
         <v>10</v>
       </c>
@@ -16448,7 +16456,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="172" spans="1:10">
+    <row r="172" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
         <v>10</v>
       </c>
@@ -16480,7 +16488,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="173" spans="1:10">
+    <row r="173" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="s">
         <v>10</v>
       </c>
@@ -16512,7 +16520,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="174" spans="1:10">
+    <row r="174" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
         <v>10</v>
       </c>
@@ -16544,7 +16552,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="175" spans="1:10">
+    <row r="175" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
         <v>10</v>
       </c>
@@ -16576,7 +16584,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="176" spans="1:10">
+    <row r="176" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
         <v>10</v>
       </c>
@@ -16608,7 +16616,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="177" spans="1:10">
+    <row r="177" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="s">
         <v>10</v>
       </c>
@@ -16640,7 +16648,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="178" spans="1:10">
+    <row r="178" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
         <v>10</v>
       </c>
@@ -16672,7 +16680,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="179" spans="1:10">
+    <row r="179" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="s">
         <v>10</v>
       </c>
@@ -16704,7 +16712,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="180" spans="1:10">
+    <row r="180" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
         <v>10</v>
       </c>
@@ -16736,7 +16744,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="181" spans="1:10">
+    <row r="181" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
         <v>10</v>
       </c>
@@ -16768,7 +16776,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="182" spans="1:10">
+    <row r="182" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
         <v>10</v>
       </c>
@@ -16800,7 +16808,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="183" spans="1:10">
+    <row r="183" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A183" s="2" t="s">
         <v>10</v>
       </c>
@@ -16832,7 +16840,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="184" spans="1:10">
+    <row r="184" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="s">
         <v>10</v>
       </c>
@@ -16864,7 +16872,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="185" spans="1:10">
+    <row r="185" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A185" s="2" t="s">
         <v>10</v>
       </c>
@@ -16896,7 +16904,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="186" spans="1:10">
+    <row r="186" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
         <v>10</v>
       </c>
@@ -16928,7 +16936,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="187" spans="1:10">
+    <row r="187" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A187" s="2" t="s">
         <v>10</v>
       </c>
@@ -16960,7 +16968,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="188" spans="1:10">
+    <row r="188" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A188" s="2" t="s">
         <v>10</v>
       </c>
@@ -16992,7 +17000,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="189" spans="1:10">
+    <row r="189" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A189" s="2" t="s">
         <v>10</v>
       </c>
@@ -17024,7 +17032,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="190" spans="1:10">
+    <row r="190" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
         <v>10</v>
       </c>
@@ -17056,7 +17064,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="191" spans="1:10">
+    <row r="191" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A191" s="2" t="s">
         <v>10</v>
       </c>
@@ -17088,7 +17096,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="192" spans="1:10">
+    <row r="192" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A192" s="2" t="s">
         <v>10</v>
       </c>
@@ -17120,7 +17128,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="193" spans="1:10">
+    <row r="193" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A193" s="2" t="s">
         <v>10</v>
       </c>
@@ -17152,7 +17160,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="194" spans="1:10">
+    <row r="194" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
         <v>10</v>
       </c>
@@ -17184,7 +17192,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="195" spans="1:10">
+    <row r="195" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A195" s="2" t="s">
         <v>10</v>
       </c>
@@ -17216,7 +17224,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="196" spans="1:10">
+    <row r="196" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A196" s="2" t="s">
         <v>10</v>
       </c>
@@ -17248,7 +17256,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="197" spans="1:10">
+    <row r="197" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A197" s="2" t="s">
         <v>10</v>
       </c>
@@ -17280,7 +17288,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="198" spans="1:10">
+    <row r="198" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
         <v>10</v>
       </c>
@@ -17312,7 +17320,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="199" spans="1:10">
+    <row r="199" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A199" s="2" t="s">
         <v>10</v>
       </c>
@@ -17344,7 +17352,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="200" spans="1:10">
+    <row r="200" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A200" s="2" t="s">
         <v>10</v>
       </c>
@@ -17376,7 +17384,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="201" spans="1:10">
+    <row r="201" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A201" s="2" t="s">
         <v>10</v>
       </c>
@@ -17408,7 +17416,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="202" spans="1:10">
+    <row r="202" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A202" s="2" t="s">
         <v>10</v>
       </c>
@@ -17440,7 +17448,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="203" spans="1:10">
+    <row r="203" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A203" s="2" t="s">
         <v>10</v>
       </c>
@@ -17472,7 +17480,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="204" spans="1:10">
+    <row r="204" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A204" s="2" t="s">
         <v>10</v>
       </c>
@@ -17504,7 +17512,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="205" spans="1:10">
+    <row r="205" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A205" s="2" t="s">
         <v>10</v>
       </c>
@@ -17536,7 +17544,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="206" spans="1:10">
+    <row r="206" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A206" s="2" t="s">
         <v>10</v>
       </c>
@@ -17568,7 +17576,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="207" spans="1:10">
+    <row r="207" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A207" s="2" t="s">
         <v>10</v>
       </c>
@@ -17600,7 +17608,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="208" spans="1:10">
+    <row r="208" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A208" s="2" t="s">
         <v>10</v>
       </c>
@@ -17632,7 +17640,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="209" spans="1:10">
+    <row r="209" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A209" s="2" t="s">
         <v>10</v>
       </c>
@@ -17664,7 +17672,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="210" spans="1:10">
+    <row r="210" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="s">
         <v>10</v>
       </c>
@@ -17696,7 +17704,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="211" spans="1:10">
+    <row r="211" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A211" s="2" t="s">
         <v>10</v>
       </c>
@@ -17728,7 +17736,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="212" spans="1:10">
+    <row r="212" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A212" s="2" t="s">
         <v>10</v>
       </c>
@@ -17760,7 +17768,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="213" spans="1:10">
+    <row r="213" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A213" s="2" t="s">
         <v>10</v>
       </c>
@@ -17792,7 +17800,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="214" spans="1:10">
+    <row r="214" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A214" s="2" t="s">
         <v>10</v>
       </c>
@@ -17824,7 +17832,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="215" spans="1:10">
+    <row r="215" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A215" s="2" t="s">
         <v>10</v>
       </c>
@@ -17856,7 +17864,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="216" spans="1:10">
+    <row r="216" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A216" s="2" t="s">
         <v>10</v>
       </c>
@@ -17888,7 +17896,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="217" spans="1:10">
+    <row r="217" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A217" s="2" t="s">
         <v>10</v>
       </c>
@@ -17920,7 +17928,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="218" spans="1:10">
+    <row r="218" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A218" s="2" t="s">
         <v>10</v>
       </c>
@@ -17952,7 +17960,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="219" spans="1:10">
+    <row r="219" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A219" s="2" t="s">
         <v>10</v>
       </c>
@@ -17984,7 +17992,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="220" spans="1:10">
+    <row r="220" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A220" s="2" t="s">
         <v>10</v>
       </c>
@@ -18016,7 +18024,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="221" spans="1:10">
+    <row r="221" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A221" s="2" t="s">
         <v>10</v>
       </c>
@@ -18048,7 +18056,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="222" spans="1:10">
+    <row r="222" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A222" s="2" t="s">
         <v>10</v>
       </c>
@@ -18080,7 +18088,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="223" spans="1:10">
+    <row r="223" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A223" s="2" t="s">
         <v>10</v>
       </c>
@@ -18112,7 +18120,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="224" spans="1:10">
+    <row r="224" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A224" s="2" t="s">
         <v>10</v>
       </c>
@@ -18144,7 +18152,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="225" spans="1:10">
+    <row r="225" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A225" s="2" t="s">
         <v>10</v>
       </c>
@@ -18176,7 +18184,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="226" spans="1:10">
+    <row r="226" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A226" s="2" t="s">
         <v>10</v>
       </c>
@@ -18208,7 +18216,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="227" spans="1:10">
+    <row r="227" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A227" s="2" t="s">
         <v>10</v>
       </c>
@@ -18240,7 +18248,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="228" spans="1:10">
+    <row r="228" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A228" s="2" t="s">
         <v>10</v>
       </c>
@@ -18272,7 +18280,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="229" spans="1:10">
+    <row r="229" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A229" s="2" t="s">
         <v>10</v>
       </c>
@@ -18304,7 +18312,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="230" spans="1:10">
+    <row r="230" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A230" s="2" t="s">
         <v>10</v>
       </c>
@@ -18336,7 +18344,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="231" spans="1:10">
+    <row r="231" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A231" s="2" t="s">
         <v>10</v>
       </c>
@@ -18368,7 +18376,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="232" spans="1:10">
+    <row r="232" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A232" s="2" t="s">
         <v>10</v>
       </c>
@@ -18400,7 +18408,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="233" spans="1:10">
+    <row r="233" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A233" s="2" t="s">
         <v>10</v>
       </c>
@@ -18432,7 +18440,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="234" spans="1:10">
+    <row r="234" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A234" s="2" t="s">
         <v>10</v>
       </c>
@@ -18464,7 +18472,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="235" spans="1:10">
+    <row r="235" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A235" s="2" t="s">
         <v>10</v>
       </c>
@@ -18496,7 +18504,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="236" spans="1:10">
+    <row r="236" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A236" s="2" t="s">
         <v>10</v>
       </c>
@@ -18528,7 +18536,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="237" spans="1:10">
+    <row r="237" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A237" s="2" t="s">
         <v>10</v>
       </c>
@@ -18560,7 +18568,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="238" spans="1:10">
+    <row r="238" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A238" s="2" t="s">
         <v>10</v>
       </c>
@@ -18592,7 +18600,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="239" spans="1:10">
+    <row r="239" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A239" s="2" t="s">
         <v>10</v>
       </c>
@@ -18624,7 +18632,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="240" spans="1:10">
+    <row r="240" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A240" s="2" t="s">
         <v>10</v>
       </c>
@@ -18656,7 +18664,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="241" spans="1:10">
+    <row r="241" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A241" s="2" t="s">
         <v>10</v>
       </c>
@@ -18688,7 +18696,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="242" spans="1:10">
+    <row r="242" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A242" s="2" t="s">
         <v>10</v>
       </c>
@@ -18720,7 +18728,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="243" spans="1:10">
+    <row r="243" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A243" s="2" t="s">
         <v>10</v>
       </c>
@@ -18752,7 +18760,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="244" spans="1:10">
+    <row r="244" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A244" s="2" t="s">
         <v>10</v>
       </c>
@@ -18784,7 +18792,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="245" spans="1:10">
+    <row r="245" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A245" s="2" t="s">
         <v>10</v>
       </c>
@@ -18816,7 +18824,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="246" spans="1:10">
+    <row r="246" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A246" s="2" t="s">
         <v>10</v>
       </c>
@@ -18848,7 +18856,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="247" spans="1:10">
+    <row r="247" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A247" s="2" t="s">
         <v>10</v>
       </c>
@@ -18880,7 +18888,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="248" spans="1:10">
+    <row r="248" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A248" s="2" t="s">
         <v>10</v>
       </c>
@@ -18912,7 +18920,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="249" spans="1:10">
+    <row r="249" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A249" s="2" t="s">
         <v>10</v>
       </c>
@@ -18944,7 +18952,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="250" spans="1:10">
+    <row r="250" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A250" s="2" t="s">
         <v>10</v>
       </c>
@@ -18976,7 +18984,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="251" spans="1:10">
+    <row r="251" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A251" s="2" t="s">
         <v>10</v>
       </c>
@@ -19008,7 +19016,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="252" spans="1:10">
+    <row r="252" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A252" s="2" t="s">
         <v>10</v>
       </c>
@@ -19040,7 +19048,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="253" spans="1:10">
+    <row r="253" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A253" s="2" t="s">
         <v>10</v>
       </c>
@@ -19072,7 +19080,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="254" spans="1:10">
+    <row r="254" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A254" s="2" t="s">
         <v>10</v>
       </c>
@@ -19104,7 +19112,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="255" spans="1:10">
+    <row r="255" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A255" s="2" t="s">
         <v>10</v>
       </c>
@@ -19136,7 +19144,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="256" spans="1:10">
+    <row r="256" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A256" s="2" t="s">
         <v>10</v>
       </c>
@@ -19168,7 +19176,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="257" spans="1:10">
+    <row r="257" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A257" s="2" t="s">
         <v>10</v>
       </c>
@@ -19200,7 +19208,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="258" spans="1:10">
+    <row r="258" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A258" s="2" t="s">
         <v>10</v>
       </c>
@@ -19232,7 +19240,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="259" spans="1:10">
+    <row r="259" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A259" s="2" t="s">
         <v>10</v>
       </c>
@@ -19264,7 +19272,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="260" spans="1:10">
+    <row r="260" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A260" s="2" t="s">
         <v>10</v>
       </c>
@@ -19296,7 +19304,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="261" spans="1:10">
+    <row r="261" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A261" s="2" t="s">
         <v>10</v>
       </c>
@@ -19328,7 +19336,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="262" spans="1:10">
+    <row r="262" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A262" s="2" t="s">
         <v>10</v>
       </c>
@@ -19360,7 +19368,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="263" spans="1:10">
+    <row r="263" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A263" s="2" t="s">
         <v>10</v>
       </c>
@@ -19392,7 +19400,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="264" spans="1:10">
+    <row r="264" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A264" s="2" t="s">
         <v>10</v>
       </c>
@@ -19424,7 +19432,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="265" spans="1:10">
+    <row r="265" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A265" s="2" t="s">
         <v>10</v>
       </c>
@@ -19456,7 +19464,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="266" spans="1:10">
+    <row r="266" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A266" s="2" t="s">
         <v>10</v>
       </c>
@@ -19488,7 +19496,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="267" spans="1:10">
+    <row r="267" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A267" s="2" t="s">
         <v>10</v>
       </c>
@@ -19520,7 +19528,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="268" spans="1:10">
+    <row r="268" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A268" s="2" t="s">
         <v>10</v>
       </c>
@@ -19552,7 +19560,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="269" spans="1:10">
+    <row r="269" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A269" s="2" t="s">
         <v>10</v>
       </c>
@@ -19584,7 +19592,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="270" spans="1:10">
+    <row r="270" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A270" s="2" t="s">
         <v>10</v>
       </c>
@@ -19616,7 +19624,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="271" spans="1:10">
+    <row r="271" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A271" s="2" t="s">
         <v>10</v>
       </c>
@@ -19648,7 +19656,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="272" spans="1:10">
+    <row r="272" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A272" s="2" t="s">
         <v>10</v>
       </c>
@@ -19680,7 +19688,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="273" spans="1:10">
+    <row r="273" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A273" s="2" t="s">
         <v>10</v>
       </c>
@@ -19712,7 +19720,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="274" spans="1:10">
+    <row r="274" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A274" s="2" t="s">
         <v>10</v>
       </c>
@@ -19744,7 +19752,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="275" spans="1:10">
+    <row r="275" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A275" s="2" t="s">
         <v>10</v>
       </c>
@@ -19776,7 +19784,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="276" spans="1:10">
+    <row r="276" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A276" s="2" t="s">
         <v>10</v>
       </c>
@@ -19808,7 +19816,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="277" spans="1:10">
+    <row r="277" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A277" s="2" t="s">
         <v>10</v>
       </c>
@@ -19840,7 +19848,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="278" spans="1:10">
+    <row r="278" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A278" s="2" t="s">
         <v>10</v>
       </c>
@@ -19872,7 +19880,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="279" spans="1:10">
+    <row r="279" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A279" s="2" t="s">
         <v>10</v>
       </c>
@@ -19904,7 +19912,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="280" spans="1:10">
+    <row r="280" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A280" s="2" t="s">
         <v>10</v>
       </c>
@@ -19936,7 +19944,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="281" spans="1:10">
+    <row r="281" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A281" s="2" t="s">
         <v>10</v>
       </c>
@@ -19968,7 +19976,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="282" spans="1:10">
+    <row r="282" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A282" s="2" t="s">
         <v>10</v>
       </c>
@@ -20000,7 +20008,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="283" spans="1:10">
+    <row r="283" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A283" s="2" t="s">
         <v>10</v>
       </c>
@@ -20032,7 +20040,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="284" spans="1:10">
+    <row r="284" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A284" s="2" t="s">
         <v>10</v>
       </c>
@@ -20064,7 +20072,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="285" spans="1:10">
+    <row r="285" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A285" s="2" t="s">
         <v>10</v>
       </c>
@@ -20096,7 +20104,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="286" spans="1:10">
+    <row r="286" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A286" s="2" t="s">
         <v>10</v>
       </c>
@@ -20128,7 +20136,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="287" spans="1:10">
+    <row r="287" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A287" s="2" t="s">
         <v>10</v>
       </c>
@@ -20160,7 +20168,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="288" spans="1:10">
+    <row r="288" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A288" s="2" t="s">
         <v>10</v>
       </c>
@@ -20192,7 +20200,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="289" spans="1:10">
+    <row r="289" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A289" s="2" t="s">
         <v>10</v>
       </c>
@@ -20224,7 +20232,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="290" spans="1:10">
+    <row r="290" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A290" s="2" t="s">
         <v>10</v>
       </c>
@@ -20256,7 +20264,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="291" spans="1:10">
+    <row r="291" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A291" s="2" t="s">
         <v>10</v>
       </c>
@@ -20288,7 +20296,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="292" spans="1:10">
+    <row r="292" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A292" s="2" t="s">
         <v>10</v>
       </c>
@@ -20320,7 +20328,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="293" spans="1:10">
+    <row r="293" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A293" s="2" t="s">
         <v>10</v>
       </c>
@@ -20352,7 +20360,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="294" spans="1:10">
+    <row r="294" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A294" s="2" t="s">
         <v>10</v>
       </c>
@@ -20384,7 +20392,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="295" spans="1:10">
+    <row r="295" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A295" s="2" t="s">
         <v>10</v>
       </c>
@@ -20416,7 +20424,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="296" spans="1:10">
+    <row r="296" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A296" s="2" t="s">
         <v>10</v>
       </c>
@@ -20448,7 +20456,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="297" spans="1:10">
+    <row r="297" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A297" s="2" t="s">
         <v>10</v>
       </c>
@@ -20480,7 +20488,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="298" spans="1:10">
+    <row r="298" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A298" s="2" t="s">
         <v>10</v>
       </c>
@@ -20512,7 +20520,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="299" spans="1:10">
+    <row r="299" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A299" s="2" t="s">
         <v>10</v>
       </c>
@@ -20544,7 +20552,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="300" spans="1:10">
+    <row r="300" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A300" s="2" t="s">
         <v>10</v>
       </c>
@@ -20576,7 +20584,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="301" spans="1:10">
+    <row r="301" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A301" s="2" t="s">
         <v>10</v>
       </c>
@@ -20608,7 +20616,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="302" spans="1:10">
+    <row r="302" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A302" s="2" t="s">
         <v>10</v>
       </c>
@@ -20640,7 +20648,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="303" spans="1:10">
+    <row r="303" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A303" s="2" t="s">
         <v>10</v>
       </c>
@@ -20672,7 +20680,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="304" spans="1:10">
+    <row r="304" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A304" s="2" t="s">
         <v>10</v>
       </c>
@@ -20704,7 +20712,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="305" spans="1:10">
+    <row r="305" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A305" s="2" t="s">
         <v>10</v>
       </c>
@@ -20736,7 +20744,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="306" spans="1:10">
+    <row r="306" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A306" s="2" t="s">
         <v>10</v>
       </c>
@@ -20768,7 +20776,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="307" spans="1:10">
+    <row r="307" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A307" s="2" t="s">
         <v>10</v>
       </c>
@@ -20800,7 +20808,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="308" spans="1:10">
+    <row r="308" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A308" s="2" t="s">
         <v>10</v>
       </c>
@@ -20832,7 +20840,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="309" spans="1:10">
+    <row r="309" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A309" s="2" t="s">
         <v>10</v>
       </c>
@@ -20864,7 +20872,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="310" spans="1:10">
+    <row r="310" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A310" s="2" t="s">
         <v>10</v>
       </c>
@@ -20896,7 +20904,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="311" spans="1:10">
+    <row r="311" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A311" s="2" t="s">
         <v>10</v>
       </c>
@@ -20928,7 +20936,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="312" spans="1:10">
+    <row r="312" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A312" s="2" t="s">
         <v>10</v>
       </c>
@@ -20960,7 +20968,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="313" spans="1:10">
+    <row r="313" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A313" s="2" t="s">
         <v>10</v>
       </c>
@@ -20992,7 +21000,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="314" spans="1:10">
+    <row r="314" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A314" s="2" t="s">
         <v>10</v>
       </c>
@@ -21024,7 +21032,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="315" spans="1:10">
+    <row r="315" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A315" s="2" t="s">
         <v>10</v>
       </c>
@@ -21056,7 +21064,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="316" spans="1:10">
+    <row r="316" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A316" s="2" t="s">
         <v>10</v>
       </c>
@@ -21088,7 +21096,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="317" spans="1:10">
+    <row r="317" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A317" s="2" t="s">
         <v>10</v>
       </c>
@@ -21120,7 +21128,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="318" spans="1:10">
+    <row r="318" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A318" s="2" t="s">
         <v>10</v>
       </c>
@@ -21152,7 +21160,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="319" spans="1:10">
+    <row r="319" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A319" s="2" t="s">
         <v>10</v>
       </c>
@@ -21184,7 +21192,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="320" spans="1:10">
+    <row r="320" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A320" s="2" t="s">
         <v>10</v>
       </c>
@@ -21216,7 +21224,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="321" spans="1:10">
+    <row r="321" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A321" s="2" t="s">
         <v>10</v>
       </c>
@@ -21248,7 +21256,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="322" spans="1:10">
+    <row r="322" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A322" s="2" t="s">
         <v>10</v>
       </c>
@@ -21280,7 +21288,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="323" spans="1:10">
+    <row r="323" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A323" s="2" t="s">
         <v>10</v>
       </c>
@@ -21312,7 +21320,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="324" spans="1:10">
+    <row r="324" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A324" s="2" t="s">
         <v>10</v>
       </c>
@@ -21344,7 +21352,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="325" spans="1:10">
+    <row r="325" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A325" s="2" t="s">
         <v>10</v>
       </c>
@@ -21376,7 +21384,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="326" spans="1:10">
+    <row r="326" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A326" s="2" t="s">
         <v>10</v>
       </c>
@@ -21408,7 +21416,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="327" spans="1:10">
+    <row r="327" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A327" s="2" t="s">
         <v>10</v>
       </c>
@@ -21440,7 +21448,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="328" spans="1:10">
+    <row r="328" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A328" s="2" t="s">
         <v>10</v>
       </c>
@@ -21472,7 +21480,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="329" spans="1:10">
+    <row r="329" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A329" s="2" t="s">
         <v>10</v>
       </c>
@@ -21504,7 +21512,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="330" spans="1:10">
+    <row r="330" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A330" s="2" t="s">
         <v>10</v>
       </c>
@@ -21536,7 +21544,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="331" spans="1:10">
+    <row r="331" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A331" s="2" t="s">
         <v>10</v>
       </c>
@@ -21568,7 +21576,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="332" spans="1:10">
+    <row r="332" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A332" s="2" t="s">
         <v>10</v>
       </c>
@@ -21600,7 +21608,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="333" spans="1:10">
+    <row r="333" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A333" s="2" t="s">
         <v>10</v>
       </c>
@@ -21632,7 +21640,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="334" spans="1:10">
+    <row r="334" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A334" s="2" t="s">
         <v>10</v>
       </c>
@@ -21664,7 +21672,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="335" spans="1:10">
+    <row r="335" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A335" s="2" t="s">
         <v>10</v>
       </c>
@@ -21696,7 +21704,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="336" spans="1:10">
+    <row r="336" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A336" s="2" t="s">
         <v>10</v>
       </c>
@@ -21728,7 +21736,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="337" spans="1:10">
+    <row r="337" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A337" s="2" t="s">
         <v>10</v>
       </c>
@@ -21760,7 +21768,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="338" spans="1:10">
+    <row r="338" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A338" s="2" t="s">
         <v>10</v>
       </c>
@@ -21792,7 +21800,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="339" spans="1:10">
+    <row r="339" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A339" s="2" t="s">
         <v>10</v>
       </c>
@@ -21824,7 +21832,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="340" spans="1:10">
+    <row r="340" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A340" s="2" t="s">
         <v>10</v>
       </c>
@@ -21856,7 +21864,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="341" spans="1:10">
+    <row r="341" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A341" s="2" t="s">
         <v>10</v>
       </c>
@@ -21888,7 +21896,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="342" spans="1:10">
+    <row r="342" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A342" s="2" t="s">
         <v>10</v>
       </c>
@@ -21920,7 +21928,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="343" spans="1:10">
+    <row r="343" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A343" s="2" t="s">
         <v>10</v>
       </c>
@@ -21952,7 +21960,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="344" spans="1:10">
+    <row r="344" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A344" s="2" t="s">
         <v>10</v>
       </c>
@@ -21984,7 +21992,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="345" spans="1:10">
+    <row r="345" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A345" s="2" t="s">
         <v>10</v>
       </c>
@@ -22016,7 +22024,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="346" spans="1:10">
+    <row r="346" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A346" s="2" t="s">
         <v>10</v>
       </c>
@@ -22048,7 +22056,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="347" spans="1:10">
+    <row r="347" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A347" s="2" t="s">
         <v>10</v>
       </c>
@@ -22080,7 +22088,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="348" spans="1:10">
+    <row r="348" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A348" s="2" t="s">
         <v>10</v>
       </c>
@@ -22112,7 +22120,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="349" spans="1:10">
+    <row r="349" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A349" s="2" t="s">
         <v>10</v>
       </c>
@@ -22144,7 +22152,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="350" spans="1:10">
+    <row r="350" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A350" s="2" t="s">
         <v>10</v>
       </c>
@@ -22176,7 +22184,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="351" spans="1:10">
+    <row r="351" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A351" s="2" t="s">
         <v>10</v>
       </c>
@@ -22208,7 +22216,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="352" spans="1:10">
+    <row r="352" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A352" s="2" t="s">
         <v>10</v>
       </c>
@@ -22240,7 +22248,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="353" spans="1:10">
+    <row r="353" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A353" s="2" t="s">
         <v>10</v>
       </c>
@@ -22272,7 +22280,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="354" spans="1:10">
+    <row r="354" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A354" s="2" t="s">
         <v>10</v>
       </c>
@@ -22304,7 +22312,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="355" spans="1:10">
+    <row r="355" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A355" s="2" t="s">
         <v>10</v>
       </c>
@@ -22336,7 +22344,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="356" spans="1:10">
+    <row r="356" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A356" s="2" t="s">
         <v>10</v>
       </c>
@@ -22368,7 +22376,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="357" spans="1:10">
+    <row r="357" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A357" s="2" t="s">
         <v>10</v>
       </c>
@@ -22400,7 +22408,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="358" spans="1:10">
+    <row r="358" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A358" s="2" t="s">
         <v>10</v>
       </c>
@@ -22432,7 +22440,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="359" spans="1:10">
+    <row r="359" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A359" s="2" t="s">
         <v>10</v>
       </c>
@@ -22464,7 +22472,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="360" spans="1:10">
+    <row r="360" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A360" s="2" t="s">
         <v>10</v>
       </c>
@@ -22496,7 +22504,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="361" spans="1:10">
+    <row r="361" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A361" s="2" t="s">
         <v>10</v>
       </c>
@@ -22528,7 +22536,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="362" spans="1:10">
+    <row r="362" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A362" s="2" t="s">
         <v>10</v>
       </c>
@@ -22560,7 +22568,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="363" spans="1:10">
+    <row r="363" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A363" s="2" t="s">
         <v>10</v>
       </c>
@@ -22592,7 +22600,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="364" spans="1:10">
+    <row r="364" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A364" s="2" t="s">
         <v>10</v>
       </c>
@@ -22624,7 +22632,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="365" spans="1:10">
+    <row r="365" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A365" s="2" t="s">
         <v>10</v>
       </c>
@@ -22656,7 +22664,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="366" spans="1:10">
+    <row r="366" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A366" s="2" t="s">
         <v>10</v>
       </c>
@@ -22688,7 +22696,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="367" spans="1:10">
+    <row r="367" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A367" s="2" t="s">
         <v>10</v>
       </c>
@@ -22720,7 +22728,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="368" spans="1:10">
+    <row r="368" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A368" s="2" t="s">
         <v>10</v>
       </c>
@@ -22752,7 +22760,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="369" spans="1:10">
+    <row r="369" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A369" s="2" t="s">
         <v>10</v>
       </c>
@@ -22784,7 +22792,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="370" spans="1:10">
+    <row r="370" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A370" s="2" t="s">
         <v>10</v>
       </c>
@@ -22816,7 +22824,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="371" spans="1:10">
+    <row r="371" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A371" s="2" t="s">
         <v>10</v>
       </c>
@@ -22848,7 +22856,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="372" spans="1:10">
+    <row r="372" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A372" s="2" t="s">
         <v>10</v>
       </c>
@@ -22880,7 +22888,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="373" spans="1:10">
+    <row r="373" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A373" s="2" t="s">
         <v>10</v>
       </c>
@@ -22912,7 +22920,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="374" spans="1:10">
+    <row r="374" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A374" s="2" t="s">
         <v>10</v>
       </c>
@@ -22944,7 +22952,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="375" spans="1:10">
+    <row r="375" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A375" s="2" t="s">
         <v>10</v>
       </c>
@@ -22976,7 +22984,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="376" spans="1:10">
+    <row r="376" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A376" s="2" t="s">
         <v>10</v>
       </c>
@@ -23008,7 +23016,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="377" spans="1:10">
+    <row r="377" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A377" s="2" t="s">
         <v>10</v>
       </c>
@@ -23040,7 +23048,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="378" spans="1:10">
+    <row r="378" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A378" s="2" t="s">
         <v>10</v>
       </c>
@@ -23072,7 +23080,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="379" spans="1:10">
+    <row r="379" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A379" s="2" t="s">
         <v>10</v>
       </c>
@@ -23104,7 +23112,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="380" spans="1:10">
+    <row r="380" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A380" s="2" t="s">
         <v>10</v>
       </c>
@@ -23136,7 +23144,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="381" spans="1:10">
+    <row r="381" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A381" s="2" t="s">
         <v>10</v>
       </c>
@@ -23168,7 +23176,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="382" spans="1:10">
+    <row r="382" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A382" s="2" t="s">
         <v>10</v>
       </c>
@@ -23200,7 +23208,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="383" spans="1:10">
+    <row r="383" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A383" s="2" t="s">
         <v>10</v>
       </c>
@@ -23232,7 +23240,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="384" spans="1:10">
+    <row r="384" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A384" s="2" t="s">
         <v>10</v>
       </c>
@@ -23264,7 +23272,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="385" spans="1:10">
+    <row r="385" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A385" s="2" t="s">
         <v>10</v>
       </c>
@@ -23296,7 +23304,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="386" spans="1:10">
+    <row r="386" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A386" s="2" t="s">
         <v>10</v>
       </c>
@@ -23328,7 +23336,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="387" spans="1:10">
+    <row r="387" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A387" s="2" t="s">
         <v>10</v>
       </c>
@@ -23360,7 +23368,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="388" spans="1:10">
+    <row r="388" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A388" s="2" t="s">
         <v>10</v>
       </c>
@@ -23392,7 +23400,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="389" spans="1:10">
+    <row r="389" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A389" s="2" t="s">
         <v>10</v>
       </c>
@@ -23424,7 +23432,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="390" spans="1:10">
+    <row r="390" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A390" s="2" t="s">
         <v>10</v>
       </c>
@@ -23456,7 +23464,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="391" spans="1:10">
+    <row r="391" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A391" s="2" t="s">
         <v>10</v>
       </c>
@@ -23488,7 +23496,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="392" spans="1:10">
+    <row r="392" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A392" s="2" t="s">
         <v>10</v>
       </c>
@@ -23520,7 +23528,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="393" spans="1:10">
+    <row r="393" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A393" s="2" t="s">
         <v>10</v>
       </c>
@@ -23552,7 +23560,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="394" spans="1:10">
+    <row r="394" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A394" s="2" t="s">
         <v>10</v>
       </c>
@@ -23584,7 +23592,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="395" spans="1:10">
+    <row r="395" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A395" s="2" t="s">
         <v>10</v>
       </c>
@@ -23616,7 +23624,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="396" spans="1:10">
+    <row r="396" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A396" s="2" t="s">
         <v>10</v>
       </c>
@@ -23648,7 +23656,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="397" spans="1:10">
+    <row r="397" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A397" s="2" t="s">
         <v>10</v>
       </c>
@@ -23680,7 +23688,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="398" spans="1:10">
+    <row r="398" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A398" s="2" t="s">
         <v>10</v>
       </c>
@@ -23712,7 +23720,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="399" spans="1:10">
+    <row r="399" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A399" s="2" t="s">
         <v>10</v>
       </c>
@@ -23744,7 +23752,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="400" spans="1:10">
+    <row r="400" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A400" s="2" t="s">
         <v>10</v>
       </c>
@@ -23776,7 +23784,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="401" spans="1:10">
+    <row r="401" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A401" s="2" t="s">
         <v>10</v>
       </c>
@@ -23808,7 +23816,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="402" spans="1:10">
+    <row r="402" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A402" s="2" t="s">
         <v>10</v>
       </c>
@@ -23840,7 +23848,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="403" spans="1:10">
+    <row r="403" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A403" s="2" t="s">
         <v>10</v>
       </c>
@@ -23872,7 +23880,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="404" spans="1:10">
+    <row r="404" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A404" s="2" t="s">
         <v>10</v>
       </c>
@@ -23904,7 +23912,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="405" spans="1:10">
+    <row r="405" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A405" s="2" t="s">
         <v>10</v>
       </c>
@@ -23936,7 +23944,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="406" spans="1:10">
+    <row r="406" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A406" s="2" t="s">
         <v>10</v>
       </c>
@@ -23968,7 +23976,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="407" spans="1:10">
+    <row r="407" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A407" s="2" t="s">
         <v>10</v>
       </c>
@@ -24000,7 +24008,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="408" spans="1:10">
+    <row r="408" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A408" s="2" t="s">
         <v>10</v>
       </c>
@@ -24032,7 +24040,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="409" spans="1:10">
+    <row r="409" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A409" s="2" t="s">
         <v>10</v>
       </c>
@@ -24064,7 +24072,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="410" spans="1:10">
+    <row r="410" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A410" s="2" t="s">
         <v>10</v>
       </c>
@@ -24096,7 +24104,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="411" spans="1:10">
+    <row r="411" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A411" s="2" t="s">
         <v>10</v>
       </c>
@@ -24128,7 +24136,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="412" spans="1:10">
+    <row r="412" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A412" s="2" t="s">
         <v>10</v>
       </c>
@@ -24160,7 +24168,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="413" spans="1:10">
+    <row r="413" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A413" s="2" t="s">
         <v>10</v>
       </c>
@@ -24192,7 +24200,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="414" spans="1:10">
+    <row r="414" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A414" s="2" t="s">
         <v>10</v>
       </c>
@@ -24224,7 +24232,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="415" spans="1:10">
+    <row r="415" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A415" s="2" t="s">
         <v>10</v>
       </c>
@@ -24256,7 +24264,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="416" spans="1:10">
+    <row r="416" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A416" s="2" t="s">
         <v>10</v>
       </c>
@@ -24288,7 +24296,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="417" spans="1:10">
+    <row r="417" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A417" s="2" t="s">
         <v>10</v>
       </c>
@@ -24320,7 +24328,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="418" spans="1:10">
+    <row r="418" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A418" s="2" t="s">
         <v>10</v>
       </c>
@@ -24352,7 +24360,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="419" spans="1:10">
+    <row r="419" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A419" s="2" t="s">
         <v>10</v>
       </c>
@@ -24384,7 +24392,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="420" spans="1:10">
+    <row r="420" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A420" s="2" t="s">
         <v>10</v>
       </c>
@@ -24416,7 +24424,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="421" spans="1:10">
+    <row r="421" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A421" s="2" t="s">
         <v>10</v>
       </c>
@@ -24448,7 +24456,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="422" spans="1:10">
+    <row r="422" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A422" s="2" t="s">
         <v>10</v>
       </c>
@@ -24480,7 +24488,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="423" spans="1:10">
+    <row r="423" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A423" s="2" t="s">
         <v>10</v>
       </c>
@@ -24512,7 +24520,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="424" spans="1:10">
+    <row r="424" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A424" s="2" t="s">
         <v>10</v>
       </c>
@@ -24544,7 +24552,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="425" spans="1:10">
+    <row r="425" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A425" s="2" t="s">
         <v>10</v>
       </c>
@@ -24576,7 +24584,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="426" spans="1:10">
+    <row r="426" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A426" s="2" t="s">
         <v>10</v>
       </c>
@@ -24608,7 +24616,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="427" spans="1:10">
+    <row r="427" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A427" s="2" t="s">
         <v>10</v>
       </c>
@@ -24640,7 +24648,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="428" spans="1:10">
+    <row r="428" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A428" s="2" t="s">
         <v>10</v>
       </c>
@@ -24672,7 +24680,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="429" spans="1:10">
+    <row r="429" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A429" s="2" t="s">
         <v>10</v>
       </c>
@@ -24704,7 +24712,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="430" spans="1:10">
+    <row r="430" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A430" s="2" t="s">
         <v>10</v>
       </c>
@@ -24736,7 +24744,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="431" spans="1:10">
+    <row r="431" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A431" s="2" t="s">
         <v>10</v>
       </c>
@@ -24768,7 +24776,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="432" spans="1:10">
+    <row r="432" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A432" s="2" t="s">
         <v>10</v>
       </c>
@@ -24800,7 +24808,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="433" spans="1:10">
+    <row r="433" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A433" s="2" t="s">
         <v>10</v>
       </c>
@@ -24832,7 +24840,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="434" spans="1:10">
+    <row r="434" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A434" s="2" t="s">
         <v>10</v>
       </c>
@@ -24864,7 +24872,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="435" spans="1:10">
+    <row r="435" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A435" s="2" t="s">
         <v>10</v>
       </c>
@@ -24896,7 +24904,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="436" spans="1:10">
+    <row r="436" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A436" s="2" t="s">
         <v>10</v>
       </c>
@@ -24928,7 +24936,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="437" spans="1:10">
+    <row r="437" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A437" s="2" t="s">
         <v>10</v>
       </c>
@@ -24960,7 +24968,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="438" spans="1:10">
+    <row r="438" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A438" s="2" t="s">
         <v>10</v>
       </c>
@@ -24992,7 +25000,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="439" spans="1:10">
+    <row r="439" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A439" s="2" t="s">
         <v>10</v>
       </c>
@@ -25024,7 +25032,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="440" spans="1:10">
+    <row r="440" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A440" s="2" t="s">
         <v>10</v>
       </c>
@@ -25056,7 +25064,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="441" spans="1:10">
+    <row r="441" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A441" s="2" t="s">
         <v>10</v>
       </c>
@@ -25088,7 +25096,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="442" spans="1:10">
+    <row r="442" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A442" s="2" t="s">
         <v>10</v>
       </c>
@@ -25120,7 +25128,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="443" spans="1:10">
+    <row r="443" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A443" s="2" t="s">
         <v>10</v>
       </c>
@@ -25152,7 +25160,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="444" spans="1:10">
+    <row r="444" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A444" s="2" t="s">
         <v>10</v>
       </c>
@@ -25184,7 +25192,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="445" spans="1:10">
+    <row r="445" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A445" s="2" t="s">
         <v>10</v>
       </c>
@@ -25216,7 +25224,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="446" spans="1:10">
+    <row r="446" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A446" s="2" t="s">
         <v>10</v>
       </c>
@@ -25248,7 +25256,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="447" spans="1:10">
+    <row r="447" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A447" s="2" t="s">
         <v>10</v>
       </c>
@@ -25280,7 +25288,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="448" spans="1:10">
+    <row r="448" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A448" s="2" t="s">
         <v>10</v>
       </c>
@@ -25312,7 +25320,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="449" spans="1:10">
+    <row r="449" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A449" s="2" t="s">
         <v>10</v>
       </c>
@@ -25344,7 +25352,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="450" spans="1:10">
+    <row r="450" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A450" s="2" t="s">
         <v>10</v>
       </c>
@@ -25376,7 +25384,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="451" spans="1:10">
+    <row r="451" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A451" s="2" t="s">
         <v>10</v>
       </c>
@@ -25408,7 +25416,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="452" spans="1:10">
+    <row r="452" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A452" s="2" t="s">
         <v>10</v>
       </c>
@@ -25440,7 +25448,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="453" spans="1:10">
+    <row r="453" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A453" s="2" t="s">
         <v>10</v>
       </c>
@@ -25472,7 +25480,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="454" spans="1:10">
+    <row r="454" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A454" s="2" t="s">
         <v>10</v>
       </c>
@@ -25504,7 +25512,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="455" spans="1:10">
+    <row r="455" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A455" s="2" t="s">
         <v>10</v>
       </c>
@@ -25536,7 +25544,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="456" spans="1:10">
+    <row r="456" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A456" s="2" t="s">
         <v>10</v>
       </c>
@@ -25568,7 +25576,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="457" spans="1:10">
+    <row r="457" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A457" s="2" t="s">
         <v>10</v>
       </c>
@@ -25600,7 +25608,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="458" spans="1:10">
+    <row r="458" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A458" s="2" t="s">
         <v>10</v>
       </c>
@@ -25632,7 +25640,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="459" spans="1:10">
+    <row r="459" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A459" s="2" t="s">
         <v>10</v>
       </c>
@@ -25664,7 +25672,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="460" spans="1:10">
+    <row r="460" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A460" s="2" t="s">
         <v>10</v>
       </c>
@@ -25696,7 +25704,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="461" spans="1:10">
+    <row r="461" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A461" s="2" t="s">
         <v>10</v>
       </c>
@@ -25728,7 +25736,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="462" spans="1:10">
+    <row r="462" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A462" s="2" t="s">
         <v>10</v>
       </c>
@@ -25760,7 +25768,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="463" spans="1:10">
+    <row r="463" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A463" s="2" t="s">
         <v>10</v>
       </c>
@@ -25792,7 +25800,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="464" spans="1:10">
+    <row r="464" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A464" s="2" t="s">
         <v>10</v>
       </c>
@@ -25824,7 +25832,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="465" spans="1:10">
+    <row r="465" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A465" s="2" t="s">
         <v>10</v>
       </c>
@@ -25856,7 +25864,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="466" spans="1:10">
+    <row r="466" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A466" s="2" t="s">
         <v>10</v>
       </c>
@@ -25888,7 +25896,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="467" spans="1:10">
+    <row r="467" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A467" s="2" t="s">
         <v>10</v>
       </c>
@@ -25920,7 +25928,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="468" spans="1:10">
+    <row r="468" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A468" s="2" t="s">
         <v>10</v>
       </c>
@@ -25952,7 +25960,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="469" spans="1:10">
+    <row r="469" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A469" s="2" t="s">
         <v>10</v>
       </c>
@@ -25984,7 +25992,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="470" spans="1:10">
+    <row r="470" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A470" s="2" t="s">
         <v>10</v>
       </c>
@@ -26016,7 +26024,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="471" spans="1:10">
+    <row r="471" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A471" s="2" t="s">
         <v>10</v>
       </c>
@@ -26048,7 +26056,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="472" spans="1:10">
+    <row r="472" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A472" s="2" t="s">
         <v>10</v>
       </c>
@@ -26080,7 +26088,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="473" spans="1:10">
+    <row r="473" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A473" s="2" t="s">
         <v>10</v>
       </c>
@@ -26112,7 +26120,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="474" spans="1:10">
+    <row r="474" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A474" s="2" t="s">
         <v>10</v>
       </c>
@@ -26144,7 +26152,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="475" spans="1:10">
+    <row r="475" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A475" s="2" t="s">
         <v>10</v>
       </c>
@@ -26176,7 +26184,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="476" spans="1:10">
+    <row r="476" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A476" s="2" t="s">
         <v>10</v>
       </c>
@@ -26208,7 +26216,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="477" spans="1:10">
+    <row r="477" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A477" s="2" t="s">
         <v>10</v>
       </c>
@@ -26240,7 +26248,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="478" spans="1:10">
+    <row r="478" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A478" s="2" t="s">
         <v>10</v>
       </c>
@@ -26272,7 +26280,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="479" spans="1:10">
+    <row r="479" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A479" s="2" t="s">
         <v>10</v>
       </c>
@@ -26304,7 +26312,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="480" spans="1:10">
+    <row r="480" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A480" s="2" t="s">
         <v>10</v>
       </c>
@@ -26336,7 +26344,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="481" spans="1:10">
+    <row r="481" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A481" s="2" t="s">
         <v>10</v>
       </c>
@@ -26368,7 +26376,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="482" spans="1:10">
+    <row r="482" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A482" s="2" t="s">
         <v>10</v>
       </c>
@@ -26400,7 +26408,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="483" spans="1:10">
+    <row r="483" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A483" s="2" t="s">
         <v>10</v>
       </c>
@@ -26432,7 +26440,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="484" spans="1:10">
+    <row r="484" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A484" s="2" t="s">
         <v>10</v>
       </c>
@@ -26464,7 +26472,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="485" spans="1:10">
+    <row r="485" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A485" s="2" t="s">
         <v>10</v>
       </c>
@@ -26496,7 +26504,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="486" spans="1:10">
+    <row r="486" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A486" s="2" t="s">
         <v>10</v>
       </c>
@@ -26528,7 +26536,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="487" spans="1:10">
+    <row r="487" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A487" s="2" t="s">
         <v>10</v>
       </c>
@@ -26560,7 +26568,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="488" spans="1:10">
+    <row r="488" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A488" s="2" t="s">
         <v>10</v>
       </c>
@@ -26592,7 +26600,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="489" spans="1:10">
+    <row r="489" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A489" s="2" t="s">
         <v>10</v>
       </c>
@@ -26624,7 +26632,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="490" spans="1:10">
+    <row r="490" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A490" s="2" t="s">
         <v>10</v>
       </c>
@@ -26656,7 +26664,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="491" spans="1:10">
+    <row r="491" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A491" s="2" t="s">
         <v>10</v>
       </c>
@@ -26688,7 +26696,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="492" spans="1:10">
+    <row r="492" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A492" s="2" t="s">
         <v>10</v>
       </c>
@@ -26720,7 +26728,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="493" spans="1:10">
+    <row r="493" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A493" s="2" t="s">
         <v>10</v>
       </c>
@@ -26752,7 +26760,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="494" spans="1:10">
+    <row r="494" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A494" s="2" t="s">
         <v>10</v>
       </c>
@@ -26784,7 +26792,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="495" spans="1:10">
+    <row r="495" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A495" s="2" t="s">
         <v>10</v>
       </c>
@@ -26816,7 +26824,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="496" spans="1:10">
+    <row r="496" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A496" s="2" t="s">
         <v>10</v>
       </c>
@@ -26848,7 +26856,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="497" spans="1:10">
+    <row r="497" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A497" s="2" t="s">
         <v>10</v>
       </c>
@@ -26880,7 +26888,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="498" spans="1:10">
+    <row r="498" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A498" s="2" t="s">
         <v>10</v>
       </c>
@@ -26912,7 +26920,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="499" spans="1:10">
+    <row r="499" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A499" s="2" t="s">
         <v>10</v>
       </c>
@@ -26944,7 +26952,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="500" spans="1:10">
+    <row r="500" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A500" s="2" t="s">
         <v>10</v>
       </c>
@@ -26976,7 +26984,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="501" spans="1:10">
+    <row r="501" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A501" s="2" t="s">
         <v>10</v>
       </c>
@@ -27008,7 +27016,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="502" spans="1:10">
+    <row r="502" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A502" s="2" t="s">
         <v>10</v>
       </c>
@@ -27040,7 +27048,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="503" spans="1:10">
+    <row r="503" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A503" s="2" t="s">
         <v>10</v>
       </c>
@@ -27072,7 +27080,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="504" spans="1:10">
+    <row r="504" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A504" s="2" t="s">
         <v>10</v>
       </c>
@@ -27104,7 +27112,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="505" spans="1:10">
+    <row r="505" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A505" s="2" t="s">
         <v>10</v>
       </c>
@@ -27136,7 +27144,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="506" spans="1:10">
+    <row r="506" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A506" s="2" t="s">
         <v>10</v>
       </c>
@@ -27168,7 +27176,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="507" spans="1:10">
+    <row r="507" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A507" s="2" t="s">
         <v>10</v>
       </c>
@@ -27200,7 +27208,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="508" spans="1:10">
+    <row r="508" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A508" s="2" t="s">
         <v>10</v>
       </c>
@@ -27232,7 +27240,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="509" spans="1:10">
+    <row r="509" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A509" s="2" t="s">
         <v>10</v>
       </c>
@@ -27264,7 +27272,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="510" spans="1:10">
+    <row r="510" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A510" s="2" t="s">
         <v>10</v>
       </c>
@@ -27296,7 +27304,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="511" spans="1:10">
+    <row r="511" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A511" s="2" t="s">
         <v>10</v>
       </c>
@@ -27328,7 +27336,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="512" spans="1:10">
+    <row r="512" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A512" s="2" t="s">
         <v>10</v>
       </c>
@@ -27360,7 +27368,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="513" spans="1:10">
+    <row r="513" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A513" s="2" t="s">
         <v>10</v>
       </c>
@@ -27392,7 +27400,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="514" spans="1:10">
+    <row r="514" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A514" s="2" t="s">
         <v>10</v>
       </c>
@@ -27424,7 +27432,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="515" spans="1:10">
+    <row r="515" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A515" s="2" t="s">
         <v>10</v>
       </c>
@@ -27456,7 +27464,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="516" spans="1:10">
+    <row r="516" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A516" s="2" t="s">
         <v>10</v>
       </c>
@@ -27488,7 +27496,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="517" spans="1:10">
+    <row r="517" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A517" s="2" t="s">
         <v>10</v>
       </c>
@@ -27520,7 +27528,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="518" spans="1:10">
+    <row r="518" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A518" s="2" t="s">
         <v>10</v>
       </c>
@@ -27552,7 +27560,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="519" spans="1:10">
+    <row r="519" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A519" s="2" t="s">
         <v>10</v>
       </c>
@@ -27584,7 +27592,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="520" spans="1:10">
+    <row r="520" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A520" s="2" t="s">
         <v>10</v>
       </c>
@@ -27616,7 +27624,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="521" spans="1:10">
+    <row r="521" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A521" s="2" t="s">
         <v>10</v>
       </c>
@@ -27648,7 +27656,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="522" spans="1:10">
+    <row r="522" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A522" s="2" t="s">
         <v>10</v>
       </c>
@@ -27680,7 +27688,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="523" spans="1:10">
+    <row r="523" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A523" s="2" t="s">
         <v>10</v>
       </c>
@@ -27712,7 +27720,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="524" spans="1:10">
+    <row r="524" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A524" s="2" t="s">
         <v>10</v>
       </c>
@@ -27744,7 +27752,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="525" spans="1:10">
+    <row r="525" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A525" s="2" t="s">
         <v>10</v>
       </c>
@@ -27776,7 +27784,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="526" spans="1:10">
+    <row r="526" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A526" s="2" t="s">
         <v>10</v>
       </c>
@@ -27808,7 +27816,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="527" spans="1:10">
+    <row r="527" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A527" s="2" t="s">
         <v>10</v>
       </c>
@@ -27840,7 +27848,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="528" spans="1:10">
+    <row r="528" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A528" s="2" t="s">
         <v>10</v>
       </c>
@@ -27872,7 +27880,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="529" spans="1:10">
+    <row r="529" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A529" s="2" t="s">
         <v>10</v>
       </c>
@@ -27904,7 +27912,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="530" spans="1:10">
+    <row r="530" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A530" s="2" t="s">
         <v>10</v>
       </c>
@@ -27936,7 +27944,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="531" spans="1:10">
+    <row r="531" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A531" s="2" t="s">
         <v>10</v>
       </c>
@@ -27968,7 +27976,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="532" spans="1:10">
+    <row r="532" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A532" s="2" t="s">
         <v>10</v>
       </c>
@@ -28000,7 +28008,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="533" spans="1:10">
+    <row r="533" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A533" s="2" t="s">
         <v>10</v>
       </c>
@@ -28032,7 +28040,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="534" spans="1:10">
+    <row r="534" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A534" s="2" t="s">
         <v>10</v>
       </c>
@@ -28064,7 +28072,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="535" spans="1:10">
+    <row r="535" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A535" s="2" t="s">
         <v>10</v>
       </c>
@@ -28096,7 +28104,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="536" spans="1:10">
+    <row r="536" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A536" s="2" t="s">
         <v>10</v>
       </c>
@@ -28128,7 +28136,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="537" spans="1:10">
+    <row r="537" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A537" s="2" t="s">
         <v>10</v>
       </c>
@@ -28160,7 +28168,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="538" spans="1:10">
+    <row r="538" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A538" s="2" t="s">
         <v>10</v>
       </c>
@@ -28192,7 +28200,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="539" spans="1:10">
+    <row r="539" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A539" s="2" t="s">
         <v>10</v>
       </c>
@@ -28224,7 +28232,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="540" spans="1:10">
+    <row r="540" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A540" s="2" t="s">
         <v>10</v>
       </c>
@@ -28256,7 +28264,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="541" spans="1:10">
+    <row r="541" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A541" s="2" t="s">
         <v>10</v>
       </c>
@@ -28288,7 +28296,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="542" spans="1:10">
+    <row r="542" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A542" s="2" t="s">
         <v>10</v>
       </c>
@@ -28320,7 +28328,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="543" spans="1:10">
+    <row r="543" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A543" s="2" t="s">
         <v>10</v>
       </c>
@@ -28352,7 +28360,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="544" spans="1:10">
+    <row r="544" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A544" s="2" t="s">
         <v>10</v>
       </c>
@@ -28384,7 +28392,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="545" spans="1:10">
+    <row r="545" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A545" s="2" t="s">
         <v>10</v>
       </c>
@@ -28416,7 +28424,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="546" spans="1:10">
+    <row r="546" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A546" s="2" t="s">
         <v>10</v>
       </c>
@@ -28448,7 +28456,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="547" spans="1:10">
+    <row r="547" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A547" s="2" t="s">
         <v>10</v>
       </c>
@@ -28480,7 +28488,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="548" spans="1:10">
+    <row r="548" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A548" s="2" t="s">
         <v>10</v>
       </c>
@@ -28512,7 +28520,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="549" spans="1:10">
+    <row r="549" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A549" s="2" t="s">
         <v>10</v>
       </c>
@@ -28544,7 +28552,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="550" spans="1:10">
+    <row r="550" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A550" s="2" t="s">
         <v>10</v>
       </c>
@@ -28576,7 +28584,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="551" spans="1:10">
+    <row r="551" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A551" s="2" t="s">
         <v>10</v>
       </c>
@@ -28608,7 +28616,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="552" spans="1:10">
+    <row r="552" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A552" s="2" t="s">
         <v>10</v>
       </c>
@@ -28640,7 +28648,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="553" spans="1:10">
+    <row r="553" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A553" s="2" t="s">
         <v>10</v>
       </c>
@@ -28672,7 +28680,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="554" spans="1:10">
+    <row r="554" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A554" s="2" t="s">
         <v>10</v>
       </c>
@@ -28704,7 +28712,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="555" spans="1:10">
+    <row r="555" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A555" s="2" t="s">
         <v>10</v>
       </c>
@@ -28736,7 +28744,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="556" spans="1:10">
+    <row r="556" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A556" s="2" t="s">
         <v>10</v>
       </c>
@@ -28768,7 +28776,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="557" spans="1:10">
+    <row r="557" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A557" s="2" t="s">
         <v>10</v>
       </c>
@@ -28800,7 +28808,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="558" spans="1:10">
+    <row r="558" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A558" s="2" t="s">
         <v>10</v>
       </c>
@@ -28832,7 +28840,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="559" spans="1:10">
+    <row r="559" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A559" s="2" t="s">
         <v>10</v>
       </c>
@@ -28864,7 +28872,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="560" spans="1:10">
+    <row r="560" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A560" s="2" t="s">
         <v>10</v>
       </c>
@@ -28896,7 +28904,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="561" spans="1:10">
+    <row r="561" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A561" s="2" t="s">
         <v>10</v>
       </c>
@@ -28928,7 +28936,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="562" spans="1:10">
+    <row r="562" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A562" s="2" t="s">
         <v>10</v>
       </c>
@@ -28960,7 +28968,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="563" spans="1:10">
+    <row r="563" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A563" s="2" t="s">
         <v>10</v>
       </c>
@@ -28992,7 +29000,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="564" spans="1:10">
+    <row r="564" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A564" s="2" t="s">
         <v>10</v>
       </c>
@@ -29024,7 +29032,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="565" spans="1:10">
+    <row r="565" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A565" s="2" t="s">
         <v>10</v>
       </c>
@@ -29056,7 +29064,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="566" spans="1:10">
+    <row r="566" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A566" s="2" t="s">
         <v>10</v>
       </c>
@@ -29088,7 +29096,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="567" spans="1:10">
+    <row r="567" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A567" s="2" t="s">
         <v>10</v>
       </c>
@@ -29120,7 +29128,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="568" spans="1:10">
+    <row r="568" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A568" s="2" t="s">
         <v>10</v>
       </c>
@@ -29152,7 +29160,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="569" spans="1:10">
+    <row r="569" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A569" s="2" t="s">
         <v>10</v>
       </c>
@@ -29184,7 +29192,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="570" spans="1:10">
+    <row r="570" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A570" s="2" t="s">
         <v>10</v>
       </c>
@@ -29216,7 +29224,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="571" spans="1:10">
+    <row r="571" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A571" s="2" t="s">
         <v>10</v>
       </c>
@@ -29248,7 +29256,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="572" spans="1:10">
+    <row r="572" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A572" s="2" t="s">
         <v>10</v>
       </c>
@@ -29280,7 +29288,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="573" spans="1:10">
+    <row r="573" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A573" s="2" t="s">
         <v>10</v>
       </c>
@@ -29312,7 +29320,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="574" spans="1:10">
+    <row r="574" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A574" s="2" t="s">
         <v>10</v>
       </c>
@@ -29344,7 +29352,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="575" spans="1:10">
+    <row r="575" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A575" s="2" t="s">
         <v>10</v>
       </c>
@@ -29376,7 +29384,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="576" spans="1:10">
+    <row r="576" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A576" s="2" t="s">
         <v>10</v>
       </c>
@@ -29408,7 +29416,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="577" spans="1:10">
+    <row r="577" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A577" s="2" t="s">
         <v>10</v>
       </c>
@@ -29440,7 +29448,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="578" spans="1:10">
+    <row r="578" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A578" s="2" t="s">
         <v>10</v>
       </c>
@@ -29472,7 +29480,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="579" spans="1:10">
+    <row r="579" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A579" s="2" t="s">
         <v>10</v>
       </c>
@@ -29504,7 +29512,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="580" spans="1:10">
+    <row r="580" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A580" s="2" t="s">
         <v>10</v>
       </c>
@@ -29536,7 +29544,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="581" spans="1:10">
+    <row r="581" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A581" s="2" t="s">
         <v>10</v>
       </c>
@@ -29568,7 +29576,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="582" spans="1:10">
+    <row r="582" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A582" s="2" t="s">
         <v>10</v>
       </c>
@@ -29600,7 +29608,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="583" spans="1:10">
+    <row r="583" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A583" s="2" t="s">
         <v>10</v>
       </c>
@@ -29632,7 +29640,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="584" spans="1:10">
+    <row r="584" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A584" s="2" t="s">
         <v>10</v>
       </c>
@@ -29664,7 +29672,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="585" spans="1:10">
+    <row r="585" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A585" s="2" t="s">
         <v>10</v>
       </c>
@@ -29696,7 +29704,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="586" spans="1:10">
+    <row r="586" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A586" s="2" t="s">
         <v>10</v>
       </c>
@@ -29728,7 +29736,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="587" spans="1:10">
+    <row r="587" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A587" s="2" t="s">
         <v>10</v>
       </c>
@@ -29760,7 +29768,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="588" spans="1:10">
+    <row r="588" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A588" s="2" t="s">
         <v>10</v>
       </c>
@@ -29792,7 +29800,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="589" spans="1:10">
+    <row r="589" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A589" s="2" t="s">
         <v>10</v>
       </c>
@@ -29824,7 +29832,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="590" spans="1:10">
+    <row r="590" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A590" s="2" t="s">
         <v>10</v>
       </c>
@@ -29856,7 +29864,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="591" spans="1:10">
+    <row r="591" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A591" s="2" t="s">
         <v>10</v>
       </c>
@@ -29888,7 +29896,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="592" spans="1:10">
+    <row r="592" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A592" s="2" t="s">
         <v>10</v>
       </c>
@@ -29920,7 +29928,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="593" spans="1:10">
+    <row r="593" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A593" s="2" t="s">
         <v>10</v>
       </c>
@@ -29952,7 +29960,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="594" spans="1:10">
+    <row r="594" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A594" s="2" t="s">
         <v>10</v>
       </c>
@@ -29984,7 +29992,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="595" spans="1:10">
+    <row r="595" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A595" s="2" t="s">
         <v>10</v>
       </c>
@@ -30016,7 +30024,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="596" spans="1:10">
+    <row r="596" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A596" s="2" t="s">
         <v>10</v>
       </c>
@@ -30048,7 +30056,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="597" spans="1:10">
+    <row r="597" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A597" s="2" t="s">
         <v>10</v>
       </c>
@@ -30080,7 +30088,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="598" spans="1:10">
+    <row r="598" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A598" s="2" t="s">
         <v>10</v>
       </c>
@@ -30112,7 +30120,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="599" spans="1:10">
+    <row r="599" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A599" s="2" t="s">
         <v>10</v>
       </c>
@@ -30144,7 +30152,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="600" spans="1:10">
+    <row r="600" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A600" s="2" t="s">
         <v>10</v>
       </c>
@@ -30176,7 +30184,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="601" spans="1:10">
+    <row r="601" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A601" s="2" t="s">
         <v>10</v>
       </c>
@@ -30208,7 +30216,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="602" spans="1:10">
+    <row r="602" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A602" s="2" t="s">
         <v>10</v>
       </c>
@@ -30240,7 +30248,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="603" spans="1:10">
+    <row r="603" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A603" s="2" t="s">
         <v>10</v>
       </c>
@@ -30272,7 +30280,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="604" spans="1:10">
+    <row r="604" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A604" s="2" t="s">
         <v>10</v>
       </c>
@@ -30304,7 +30312,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="605" spans="1:10">
+    <row r="605" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A605" s="2" t="s">
         <v>10</v>
       </c>
@@ -30336,7 +30344,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="606" spans="1:10">
+    <row r="606" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A606" s="2" t="s">
         <v>10</v>
       </c>
@@ -30368,7 +30376,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="607" spans="1:10">
+    <row r="607" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A607" s="2" t="s">
         <v>10</v>
       </c>
@@ -30400,7 +30408,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="608" spans="1:10">
+    <row r="608" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A608" s="2" t="s">
         <v>10</v>
       </c>
@@ -30432,7 +30440,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="609" spans="1:10">
+    <row r="609" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A609" s="2" t="s">
         <v>10</v>
       </c>
@@ -30464,7 +30472,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="610" spans="1:10">
+    <row r="610" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A610" s="2" t="s">
         <v>10</v>
       </c>
@@ -30496,7 +30504,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="611" spans="1:10">
+    <row r="611" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A611" s="2" t="s">
         <v>10</v>
       </c>
@@ -30528,7 +30536,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="612" spans="1:10">
+    <row r="612" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A612" s="2" t="s">
         <v>10</v>
       </c>
@@ -30560,7 +30568,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="613" spans="1:10">
+    <row r="613" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A613" s="2" t="s">
         <v>10</v>
       </c>
@@ -30592,7 +30600,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="614" spans="1:10">
+    <row r="614" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A614" s="2" t="s">
         <v>10</v>
       </c>
@@ -30624,7 +30632,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="615" spans="1:10">
+    <row r="615" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A615" s="2" t="s">
         <v>10</v>
       </c>
@@ -30656,7 +30664,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="616" spans="1:10">
+    <row r="616" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A616" s="2" t="s">
         <v>10</v>
       </c>
@@ -30688,7 +30696,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="617" spans="1:10">
+    <row r="617" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A617" s="2" t="s">
         <v>10</v>
       </c>
@@ -30720,7 +30728,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="618" spans="1:10">
+    <row r="618" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A618" s="2" t="s">
         <v>10</v>
       </c>
@@ -30752,7 +30760,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="619" spans="1:10">
+    <row r="619" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A619" s="2" t="s">
         <v>10</v>
       </c>
@@ -30784,7 +30792,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="620" spans="1:10">
+    <row r="620" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A620" s="2" t="s">
         <v>10</v>
       </c>
@@ -30816,7 +30824,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="621" spans="1:10">
+    <row r="621" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A621" s="2" t="s">
         <v>10</v>
       </c>
@@ -30848,7 +30856,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="622" spans="1:10">
+    <row r="622" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A622" s="2" t="s">
         <v>10</v>
       </c>
@@ -30880,7 +30888,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="623" spans="1:10">
+    <row r="623" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A623" s="2" t="s">
         <v>10</v>
       </c>
@@ -30912,7 +30920,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="624" spans="1:10">
+    <row r="624" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A624" s="2" t="s">
         <v>10</v>
       </c>
@@ -30944,7 +30952,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="625" spans="1:10">
+    <row r="625" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A625" s="2" t="s">
         <v>10</v>
       </c>
@@ -30976,7 +30984,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="626" spans="1:10">
+    <row r="626" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A626" s="2" t="s">
         <v>10</v>
       </c>
@@ -31008,7 +31016,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="627" spans="1:10">
+    <row r="627" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A627" s="2" t="s">
         <v>10</v>
       </c>
@@ -31040,7 +31048,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="628" spans="1:10">
+    <row r="628" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A628" s="2" t="s">
         <v>10</v>
       </c>
@@ -31072,7 +31080,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="629" spans="1:10">
+    <row r="629" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A629" s="2" t="s">
         <v>10</v>
       </c>
@@ -31104,7 +31112,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="630" spans="1:10">
+    <row r="630" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A630" s="2" t="s">
         <v>10</v>
       </c>
@@ -31136,7 +31144,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="631" spans="1:10">
+    <row r="631" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A631" s="2" t="s">
         <v>10</v>
       </c>
@@ -31168,7 +31176,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="632" spans="1:10">
+    <row r="632" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A632" s="2" t="s">
         <v>10</v>
       </c>
@@ -31200,7 +31208,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="633" spans="1:10">
+    <row r="633" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A633" s="2" t="s">
         <v>10</v>
       </c>
@@ -31232,7 +31240,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="634" spans="1:10">
+    <row r="634" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A634" s="2" t="s">
         <v>10</v>
       </c>
@@ -31264,7 +31272,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="635" spans="1:10">
+    <row r="635" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A635" s="2" t="s">
         <v>10</v>
       </c>
@@ -31296,7 +31304,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="636" spans="1:10">
+    <row r="636" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A636" s="2" t="s">
         <v>10</v>
       </c>
@@ -31328,7 +31336,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="637" spans="1:10">
+    <row r="637" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A637" s="2" t="s">
         <v>10</v>
       </c>
@@ -31360,7 +31368,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="638" spans="1:10">
+    <row r="638" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A638" s="2" t="s">
         <v>10</v>
       </c>
@@ -31392,7 +31400,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="639" spans="1:10">
+    <row r="639" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A639" s="2" t="s">
         <v>10</v>
       </c>
@@ -31424,7 +31432,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="640" spans="1:10">
+    <row r="640" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A640" s="2" t="s">
         <v>10</v>
       </c>
@@ -31456,7 +31464,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="641" spans="1:10">
+    <row r="641" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A641" s="2" t="s">
         <v>10</v>
       </c>
@@ -31488,7 +31496,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="642" spans="1:10">
+    <row r="642" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A642" s="2" t="s">
         <v>10</v>
       </c>
@@ -31520,7 +31528,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="643" spans="1:10">
+    <row r="643" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A643" s="2" t="s">
         <v>10</v>
       </c>
@@ -31552,7 +31560,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="644" spans="1:10">
+    <row r="644" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A644" s="2" t="s">
         <v>10</v>
       </c>
@@ -31584,7 +31592,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="645" spans="1:10">
+    <row r="645" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A645" s="2" t="s">
         <v>10</v>
       </c>
@@ -31616,7 +31624,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="646" spans="1:10">
+    <row r="646" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A646" s="2" t="s">
         <v>10</v>
       </c>
@@ -31648,7 +31656,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="647" spans="1:10">
+    <row r="647" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A647" s="2" t="s">
         <v>10</v>
       </c>
@@ -31680,7 +31688,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="648" spans="1:10">
+    <row r="648" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A648" s="2" t="s">
         <v>10</v>
       </c>
@@ -31712,7 +31720,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="649" spans="1:10">
+    <row r="649" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A649" s="2" t="s">
         <v>10</v>
       </c>
@@ -31744,7 +31752,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="650" spans="1:10">
+    <row r="650" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A650" s="2" t="s">
         <v>10</v>
       </c>
@@ -31776,7 +31784,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="651" spans="1:10">
+    <row r="651" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A651" s="2" t="s">
         <v>10</v>
       </c>
@@ -31808,7 +31816,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="652" spans="1:10">
+    <row r="652" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A652" s="2" t="s">
         <v>10</v>
       </c>
@@ -31840,7 +31848,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="653" spans="1:10">
+    <row r="653" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A653" s="2" t="s">
         <v>10</v>
       </c>
@@ -31872,7 +31880,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="654" spans="1:10">
+    <row r="654" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A654" s="2" t="s">
         <v>10</v>
       </c>
@@ -31904,7 +31912,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="655" spans="1:10">
+    <row r="655" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A655" s="2" t="s">
         <v>10</v>
       </c>
@@ -31936,7 +31944,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="656" spans="1:10">
+    <row r="656" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A656" s="2" t="s">
         <v>10</v>
       </c>
@@ -31968,7 +31976,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="657" spans="1:10">
+    <row r="657" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A657" s="2" t="s">
         <v>10</v>
       </c>
@@ -32000,7 +32008,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="658" spans="1:10">
+    <row r="658" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A658" s="2" t="s">
         <v>10</v>
       </c>
@@ -32032,7 +32040,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="659" spans="1:10">
+    <row r="659" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A659" s="2" t="s">
         <v>10</v>
       </c>
@@ -32064,7 +32072,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="660" spans="1:10">
+    <row r="660" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A660" s="2" t="s">
         <v>10</v>
       </c>
@@ -32096,7 +32104,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="661" spans="1:10">
+    <row r="661" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A661" s="2" t="s">
         <v>10</v>
       </c>
@@ -32128,7 +32136,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="662" spans="1:10">
+    <row r="662" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A662" s="2" t="s">
         <v>10</v>
       </c>
@@ -32160,7 +32168,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="663" spans="1:10">
+    <row r="663" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A663" s="2" t="s">
         <v>10</v>
       </c>
@@ -32192,7 +32200,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="664" spans="1:10">
+    <row r="664" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A664" s="2" t="s">
         <v>10</v>
       </c>
@@ -32224,7 +32232,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="665" spans="1:10">
+    <row r="665" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A665" s="2" t="s">
         <v>10</v>
       </c>
@@ -32256,7 +32264,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="666" spans="1:10">
+    <row r="666" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A666" s="2" t="s">
         <v>10</v>
       </c>
@@ -32288,7 +32296,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="667" spans="1:10">
+    <row r="667" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A667" s="2" t="s">
         <v>10</v>
       </c>
@@ -32320,7 +32328,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="668" spans="1:10">
+    <row r="668" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A668" s="2" t="s">
         <v>10</v>
       </c>
@@ -32352,7 +32360,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="669" spans="1:10">
+    <row r="669" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A669" s="2" t="s">
         <v>10</v>
       </c>
@@ -32384,7 +32392,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="670" spans="1:10">
+    <row r="670" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A670" s="2" t="s">
         <v>10</v>
       </c>
@@ -32416,7 +32424,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="671" spans="1:10">
+    <row r="671" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A671" s="2" t="s">
         <v>10</v>
       </c>
@@ -32448,7 +32456,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="672" spans="1:10">
+    <row r="672" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A672" s="2" t="s">
         <v>10</v>
       </c>
@@ -32480,7 +32488,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="673" spans="1:10">
+    <row r="673" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A673" s="2" t="s">
         <v>10</v>
       </c>
@@ -32512,7 +32520,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="674" spans="1:10">
+    <row r="674" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A674" s="2" t="s">
         <v>10</v>
       </c>
@@ -32544,7 +32552,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="675" spans="1:10">
+    <row r="675" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A675" s="2" t="s">
         <v>10</v>
       </c>
@@ -32576,7 +32584,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="676" spans="1:10">
+    <row r="676" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A676" s="2" t="s">
         <v>10</v>
       </c>
@@ -32608,7 +32616,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="677" spans="1:10">
+    <row r="677" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A677" s="2" t="s">
         <v>10</v>
       </c>
@@ -32640,7 +32648,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="678" spans="1:10">
+    <row r="678" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A678" s="2" t="s">
         <v>10</v>
       </c>
@@ -32672,7 +32680,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="679" spans="1:10">
+    <row r="679" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A679" s="2" t="s">
         <v>10</v>
       </c>
@@ -32704,7 +32712,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="680" spans="1:10">
+    <row r="680" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A680" s="2" t="s">
         <v>10</v>
       </c>
@@ -32736,7 +32744,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="681" spans="1:10">
+    <row r="681" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A681" s="2" t="s">
         <v>10</v>
       </c>
@@ -32768,7 +32776,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="682" spans="1:10">
+    <row r="682" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A682" s="2" t="s">
         <v>10</v>
       </c>
@@ -32800,7 +32808,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="683" spans="1:10">
+    <row r="683" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A683" s="2" t="s">
         <v>10</v>
       </c>
@@ -32832,7 +32840,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="684" spans="1:10">
+    <row r="684" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A684" s="2" t="s">
         <v>10</v>
       </c>
@@ -32864,7 +32872,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="685" spans="1:10">
+    <row r="685" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A685" s="2" t="s">
         <v>10</v>
       </c>
@@ -32896,7 +32904,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="686" spans="1:10">
+    <row r="686" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A686" s="2" t="s">
         <v>10</v>
       </c>
@@ -32928,7 +32936,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="687" spans="1:10">
+    <row r="687" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A687" s="2" t="s">
         <v>10</v>
       </c>
@@ -32960,7 +32968,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="688" spans="1:10">
+    <row r="688" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A688" s="2" t="s">
         <v>10</v>
       </c>
@@ -32992,7 +33000,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="689" spans="1:10">
+    <row r="689" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A689" s="2" t="s">
         <v>10</v>
       </c>
@@ -33024,7 +33032,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="690" spans="1:10">
+    <row r="690" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A690" s="2" t="s">
         <v>10</v>
       </c>
@@ -33056,7 +33064,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="691" spans="1:10">
+    <row r="691" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A691" s="2" t="s">
         <v>10</v>
       </c>
@@ -33088,7 +33096,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="692" spans="1:10">
+    <row r="692" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A692" s="2" t="s">
         <v>10</v>
       </c>
@@ -33120,7 +33128,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="693" spans="1:10">
+    <row r="693" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A693" s="2" t="s">
         <v>10</v>
       </c>
@@ -33152,7 +33160,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="694" spans="1:10">
+    <row r="694" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A694" s="2" t="s">
         <v>10</v>
       </c>
@@ -33184,7 +33192,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="695" spans="1:10">
+    <row r="695" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A695" s="2" t="s">
         <v>10</v>
       </c>
@@ -33216,7 +33224,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="696" spans="1:10">
+    <row r="696" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A696" s="2" t="s">
         <v>10</v>
       </c>
@@ -33248,7 +33256,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="697" spans="1:10">
+    <row r="697" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A697" s="2" t="s">
         <v>10</v>
       </c>
@@ -33280,7 +33288,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="698" spans="1:10">
+    <row r="698" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A698" s="2" t="s">
         <v>10</v>
       </c>
@@ -33312,7 +33320,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="699" spans="1:10">
+    <row r="699" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A699" s="2" t="s">
         <v>10</v>
       </c>
@@ -33344,7 +33352,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="700" spans="1:10">
+    <row r="700" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A700" s="2" t="s">
         <v>10</v>
       </c>
@@ -33376,7 +33384,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="701" spans="1:10">
+    <row r="701" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A701" s="2" t="s">
         <v>10</v>
       </c>
@@ -33408,7 +33416,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="702" spans="1:10">
+    <row r="702" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A702" s="2" t="s">
         <v>10</v>
       </c>
@@ -33440,7 +33448,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="703" spans="1:10">
+    <row r="703" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A703" s="2" t="s">
         <v>10</v>
       </c>
@@ -33472,7 +33480,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="704" spans="1:10">
+    <row r="704" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A704" s="2" t="s">
         <v>10</v>
       </c>
@@ -33504,7 +33512,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="705" spans="1:10">
+    <row r="705" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A705" s="2" t="s">
         <v>10</v>
       </c>
@@ -33536,7 +33544,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="706" spans="1:10">
+    <row r="706" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A706" s="2" t="s">
         <v>10</v>
       </c>
@@ -33568,7 +33576,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="707" spans="1:10">
+    <row r="707" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A707" s="2" t="s">
         <v>10</v>
       </c>
@@ -33600,7 +33608,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="708" spans="1:10">
+    <row r="708" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A708" s="2" t="s">
         <v>10</v>
       </c>
@@ -33632,7 +33640,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="709" spans="1:10">
+    <row r="709" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A709" s="2" t="s">
         <v>10</v>
       </c>
@@ -33664,7 +33672,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="710" spans="1:10">
+    <row r="710" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A710" s="2" t="s">
         <v>10</v>
       </c>
@@ -33696,7 +33704,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="711" spans="1:10">
+    <row r="711" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A711" s="2" t="s">
         <v>10</v>
       </c>
@@ -33728,7 +33736,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="712" spans="1:10">
+    <row r="712" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A712" s="2" t="s">
         <v>10</v>
       </c>
@@ -33760,7 +33768,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="713" spans="1:10">
+    <row r="713" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A713" s="2" t="s">
         <v>10</v>
       </c>
@@ -33792,7 +33800,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="714" spans="1:10">
+    <row r="714" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A714" s="2" t="s">
         <v>10</v>
       </c>
@@ -33824,7 +33832,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="715" spans="1:10">
+    <row r="715" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A715" s="2" t="s">
         <v>10</v>
       </c>
@@ -33856,7 +33864,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="716" spans="1:10">
+    <row r="716" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A716" s="2" t="s">
         <v>10</v>
       </c>
@@ -33888,7 +33896,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="717" spans="1:10">
+    <row r="717" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A717" s="2" t="s">
         <v>10</v>
       </c>
@@ -33920,7 +33928,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="718" spans="1:10">
+    <row r="718" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A718" s="2" t="s">
         <v>10</v>
       </c>
@@ -33952,7 +33960,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="719" spans="1:10">
+    <row r="719" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A719" s="2" t="s">
         <v>10</v>
       </c>
@@ -33984,7 +33992,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="720" spans="1:10">
+    <row r="720" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A720" s="2" t="s">
         <v>10</v>
       </c>
@@ -34016,7 +34024,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="721" spans="1:10">
+    <row r="721" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A721" s="2" t="s">
         <v>10</v>
       </c>
@@ -34048,7 +34056,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="722" spans="1:10">
+    <row r="722" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A722" s="2" t="s">
         <v>10</v>
       </c>
@@ -34080,7 +34088,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="723" spans="1:10">
+    <row r="723" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A723" s="2" t="s">
         <v>10</v>
       </c>
@@ -34112,7 +34120,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="724" spans="1:10">
+    <row r="724" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A724" s="2" t="s">
         <v>10</v>
       </c>
@@ -34144,7 +34152,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="725" spans="1:10">
+    <row r="725" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A725" s="2" t="s">
         <v>10</v>
       </c>
@@ -34176,7 +34184,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="726" spans="1:10">
+    <row r="726" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A726" s="2" t="s">
         <v>10</v>
       </c>
@@ -34208,7 +34216,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="727" spans="1:10">
+    <row r="727" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A727" s="2" t="s">
         <v>10</v>
       </c>
@@ -34240,7 +34248,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="728" spans="1:10">
+    <row r="728" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A728" s="2" t="s">
         <v>10</v>
       </c>
@@ -34272,7 +34280,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="729" spans="1:10">
+    <row r="729" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A729" s="2" t="s">
         <v>10</v>
       </c>
@@ -34304,7 +34312,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="730" spans="1:10">
+    <row r="730" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A730" s="2" t="s">
         <v>10</v>
       </c>
@@ -34336,7 +34344,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="731" spans="1:10">
+    <row r="731" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A731" s="2" t="s">
         <v>10</v>
       </c>
@@ -34368,7 +34376,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="732" spans="1:10">
+    <row r="732" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A732" s="2" t="s">
         <v>10</v>
       </c>
@@ -34400,7 +34408,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="733" spans="1:10">
+    <row r="733" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A733" s="2" t="s">
         <v>10</v>
       </c>
@@ -34432,7 +34440,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="734" spans="1:10">
+    <row r="734" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A734" s="2" t="s">
         <v>10</v>
       </c>
@@ -34464,7 +34472,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="735" spans="1:10">
+    <row r="735" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A735" s="2" t="s">
         <v>10</v>
       </c>
@@ -34496,7 +34504,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="736" spans="1:10">
+    <row r="736" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A736" s="2" t="s">
         <v>10</v>
       </c>
@@ -34528,7 +34536,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="737" spans="1:10">
+    <row r="737" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A737" s="2" t="s">
         <v>10</v>
       </c>
@@ -34560,7 +34568,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="738" spans="1:10">
+    <row r="738" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A738" s="2" t="s">
         <v>10</v>
       </c>
@@ -34592,7 +34600,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="739" spans="1:10">
+    <row r="739" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A739" s="2" t="s">
         <v>10</v>
       </c>
@@ -34624,7 +34632,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="740" spans="1:10">
+    <row r="740" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A740" s="2" t="s">
         <v>10</v>
       </c>
@@ -34656,7 +34664,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="741" spans="1:10">
+    <row r="741" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A741" s="2" t="s">
         <v>10</v>
       </c>
@@ -34688,7 +34696,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="742" spans="1:10">
+    <row r="742" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A742" s="2" t="s">
         <v>10</v>
       </c>
@@ -34720,7 +34728,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="743" spans="1:10">
+    <row r="743" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A743" s="2" t="s">
         <v>10</v>
       </c>
@@ -34752,7 +34760,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="744" spans="1:10">
+    <row r="744" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A744" s="2" t="s">
         <v>10</v>
       </c>
@@ -34784,7 +34792,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="745" spans="1:10">
+    <row r="745" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A745" s="2" t="s">
         <v>10</v>
       </c>
@@ -34816,7 +34824,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="746" spans="1:10">
+    <row r="746" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A746" s="2" t="s">
         <v>10</v>
       </c>
@@ -34848,7 +34856,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="747" spans="1:10">
+    <row r="747" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A747" s="2" t="s">
         <v>10</v>
       </c>
@@ -34880,7 +34888,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="748" spans="1:10">
+    <row r="748" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A748" s="2" t="s">
         <v>10</v>
       </c>
@@ -34912,7 +34920,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="749" spans="1:10">
+    <row r="749" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A749" s="2" t="s">
         <v>10</v>
       </c>
@@ -34944,7 +34952,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="750" spans="1:10">
+    <row r="750" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A750" s="2" t="s">
         <v>10</v>
       </c>
@@ -34976,7 +34984,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="751" spans="1:10">
+    <row r="751" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A751" s="2" t="s">
         <v>10</v>
       </c>
@@ -35008,7 +35016,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="752" spans="1:10">
+    <row r="752" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A752" s="2" t="s">
         <v>10</v>
       </c>
@@ -35040,7 +35048,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="753" spans="1:10">
+    <row r="753" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A753" s="2" t="s">
         <v>10</v>
       </c>
@@ -35072,7 +35080,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="754" spans="1:10">
+    <row r="754" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A754" s="2" t="s">
         <v>10</v>
       </c>
@@ -35104,7 +35112,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="755" spans="1:10">
+    <row r="755" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A755" s="2" t="s">
         <v>10</v>
       </c>
@@ -35136,7 +35144,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="756" spans="1:10">
+    <row r="756" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A756" s="2" t="s">
         <v>10</v>
       </c>
@@ -35168,7 +35176,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="757" spans="1:10">
+    <row r="757" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A757" s="2" t="s">
         <v>10</v>
       </c>
@@ -35200,7 +35208,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="758" spans="1:10">
+    <row r="758" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A758" s="2" t="s">
         <v>10</v>
       </c>
@@ -35232,7 +35240,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="759" spans="1:10">
+    <row r="759" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A759" s="2" t="s">
         <v>10</v>
       </c>
@@ -35264,7 +35272,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="760" spans="1:10">
+    <row r="760" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A760" s="2" t="s">
         <v>10</v>
       </c>
@@ -35296,7 +35304,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="761" spans="1:10">
+    <row r="761" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A761" s="2" t="s">
         <v>10</v>
       </c>
@@ -35328,7 +35336,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="762" spans="1:10">
+    <row r="762" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A762" s="2" t="s">
         <v>10</v>
       </c>
@@ -35360,7 +35368,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="763" spans="1:10">
+    <row r="763" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A763" s="2" t="s">
         <v>10</v>
       </c>
@@ -35392,7 +35400,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="764" spans="1:10">
+    <row r="764" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A764" s="2" t="s">
         <v>10</v>
       </c>
@@ -35424,7 +35432,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="765" spans="1:10">
+    <row r="765" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A765" s="2" t="s">
         <v>10</v>
       </c>
@@ -35456,7 +35464,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="766" spans="1:10">
+    <row r="766" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A766" s="2" t="s">
         <v>10</v>
       </c>
@@ -35488,7 +35496,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="767" spans="1:10">
+    <row r="767" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A767" s="2" t="s">
         <v>10</v>
       </c>
@@ -35520,7 +35528,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="768" spans="1:10">
+    <row r="768" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A768" s="2" t="s">
         <v>10</v>
       </c>
@@ -35552,7 +35560,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="769" spans="1:10">
+    <row r="769" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A769" s="2" t="s">
         <v>10</v>
       </c>
@@ -35584,7 +35592,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="770" spans="1:10">
+    <row r="770" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A770" s="2" t="s">
         <v>10</v>
       </c>
@@ -35616,7 +35624,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="771" spans="1:10">
+    <row r="771" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A771" s="2" t="s">
         <v>10</v>
       </c>
@@ -35648,7 +35656,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="772" spans="1:10">
+    <row r="772" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A772" s="2" t="s">
         <v>10</v>
       </c>
@@ -35680,7 +35688,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="773" spans="1:10">
+    <row r="773" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A773" s="2" t="s">
         <v>10</v>
       </c>
@@ -35712,7 +35720,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="774" spans="1:10">
+    <row r="774" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A774" s="2" t="s">
         <v>10</v>
       </c>
@@ -35744,7 +35752,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="775" spans="1:10">
+    <row r="775" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A775" s="2" t="s">
         <v>10</v>
       </c>
@@ -35776,7 +35784,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="776" spans="1:10">
+    <row r="776" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A776" s="2" t="s">
         <v>10</v>
       </c>
@@ -35808,7 +35816,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="777" spans="1:10">
+    <row r="777" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A777" s="2" t="s">
         <v>10</v>
       </c>
@@ -35840,7 +35848,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="778" spans="1:10">
+    <row r="778" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A778" s="2" t="s">
         <v>10</v>
       </c>
@@ -35872,7 +35880,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="779" spans="1:10">
+    <row r="779" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A779" s="2" t="s">
         <v>10</v>
       </c>
@@ -35904,7 +35912,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="780" spans="1:10">
+    <row r="780" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A780" s="2" t="s">
         <v>10</v>
       </c>
@@ -35936,7 +35944,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="781" spans="1:10">
+    <row r="781" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A781" s="2" t="s">
         <v>10</v>
       </c>
@@ -35968,7 +35976,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="782" spans="1:10">
+    <row r="782" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A782" s="2" t="s">
         <v>10</v>
       </c>
@@ -36000,7 +36008,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="783" spans="1:10">
+    <row r="783" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A783" s="2" t="s">
         <v>10</v>
       </c>
@@ -36032,7 +36040,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="784" spans="1:10">
+    <row r="784" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A784" s="2" t="s">
         <v>10</v>
       </c>
@@ -36064,7 +36072,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="785" spans="1:10">
+    <row r="785" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A785" s="2" t="s">
         <v>10</v>
       </c>
@@ -36096,7 +36104,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="786" spans="1:10">
+    <row r="786" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A786" s="2" t="s">
         <v>10</v>
       </c>
@@ -36128,7 +36136,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="787" spans="1:10">
+    <row r="787" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A787" s="2" t="s">
         <v>10</v>
       </c>
@@ -36160,7 +36168,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="788" spans="1:10">
+    <row r="788" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A788" s="2" t="s">
         <v>10</v>
       </c>
@@ -36192,7 +36200,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="789" spans="1:10">
+    <row r="789" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A789" s="2" t="s">
         <v>10</v>
       </c>
@@ -36224,7 +36232,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="790" spans="1:10">
+    <row r="790" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A790" s="2" t="s">
         <v>10</v>
       </c>
@@ -36256,7 +36264,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="791" spans="1:10">
+    <row r="791" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A791" s="2" t="s">
         <v>10</v>
       </c>
@@ -36288,7 +36296,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="792" spans="1:10">
+    <row r="792" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A792" s="2" t="s">
         <v>10</v>
       </c>
@@ -36320,7 +36328,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="793" spans="1:10">
+    <row r="793" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A793" s="2" t="s">
         <v>10</v>
       </c>
@@ -36352,7 +36360,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="794" spans="1:10">
+    <row r="794" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A794" s="2" t="s">
         <v>10</v>
       </c>
@@ -36384,7 +36392,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="795" spans="1:10">
+    <row r="795" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A795" s="2" t="s">
         <v>10</v>
       </c>
@@ -36416,7 +36424,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="796" spans="1:10">
+    <row r="796" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A796" s="2" t="s">
         <v>10</v>
       </c>
@@ -36448,7 +36456,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="797" spans="1:10">
+    <row r="797" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A797" s="2" t="s">
         <v>10</v>
       </c>
@@ -36480,7 +36488,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="798" spans="1:10">
+    <row r="798" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A798" s="2" t="s">
         <v>10</v>
       </c>
@@ -36512,7 +36520,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="799" spans="1:10">
+    <row r="799" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A799" s="2" t="s">
         <v>10</v>
       </c>
@@ -36544,7 +36552,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="800" spans="1:10">
+    <row r="800" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A800" s="2" t="s">
         <v>10</v>
       </c>
@@ -36576,7 +36584,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="801" spans="1:10">
+    <row r="801" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A801" s="2" t="s">
         <v>10</v>
       </c>
@@ -36608,7 +36616,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="802" spans="1:10">
+    <row r="802" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A802" s="2" t="s">
         <v>10</v>
       </c>
@@ -36640,7 +36648,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="803" spans="1:10">
+    <row r="803" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A803" s="2" t="s">
         <v>10</v>
       </c>
@@ -36672,7 +36680,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="804" spans="1:10">
+    <row r="804" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A804" s="2" t="s">
         <v>10</v>
       </c>
@@ -36704,7 +36712,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="805" spans="1:10">
+    <row r="805" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A805" s="2" t="s">
         <v>10</v>
       </c>
@@ -36736,7 +36744,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="806" spans="1:10">
+    <row r="806" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A806" s="2" t="s">
         <v>10</v>
       </c>
@@ -36768,7 +36776,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="807" spans="1:10">
+    <row r="807" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A807" s="2" t="s">
         <v>10</v>
       </c>
@@ -36800,7 +36808,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="808" spans="1:10">
+    <row r="808" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A808" s="2" t="s">
         <v>10</v>
       </c>
@@ -36832,7 +36840,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="809" spans="1:10">
+    <row r="809" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A809" s="2" t="s">
         <v>10</v>
       </c>
@@ -36864,7 +36872,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="810" spans="1:10">
+    <row r="810" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A810" s="2" t="s">
         <v>10</v>
       </c>
@@ -36896,7 +36904,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="811" spans="1:10">
+    <row r="811" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A811" s="2" t="s">
         <v>10</v>
       </c>
@@ -36928,7 +36936,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="812" spans="1:10">
+    <row r="812" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A812" s="2" t="s">
         <v>10</v>
       </c>
@@ -36960,7 +36968,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="813" spans="1:10">
+    <row r="813" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A813" s="2" t="s">
         <v>10</v>
       </c>
@@ -36992,7 +37000,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="814" spans="1:10">
+    <row r="814" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A814" s="2" t="s">
         <v>10</v>
       </c>
@@ -37024,7 +37032,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="815" spans="1:10">
+    <row r="815" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A815" s="2" t="s">
         <v>10</v>
       </c>
@@ -37056,7 +37064,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="816" spans="1:10">
+    <row r="816" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A816" s="2" t="s">
         <v>10</v>
       </c>
@@ -37088,7 +37096,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="817" spans="1:10">
+    <row r="817" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A817" s="2" t="s">
         <v>10</v>
       </c>
@@ -37120,7 +37128,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="818" spans="1:10">
+    <row r="818" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A818" s="2" t="s">
         <v>10</v>
       </c>
@@ -37152,7 +37160,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="819" spans="1:10">
+    <row r="819" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A819" s="2" t="s">
         <v>10</v>
       </c>
@@ -37184,7 +37192,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="820" spans="1:10">
+    <row r="820" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A820" s="2" t="s">
         <v>10</v>
       </c>
@@ -37216,7 +37224,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="821" spans="1:10">
+    <row r="821" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A821" s="2" t="s">
         <v>10</v>
       </c>
@@ -37248,7 +37256,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="822" spans="1:10">
+    <row r="822" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A822" s="2" t="s">
         <v>10</v>
       </c>
@@ -37280,7 +37288,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="823" spans="1:10">
+    <row r="823" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A823" s="2" t="s">
         <v>10</v>
       </c>
@@ -37312,7 +37320,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="824" spans="1:10">
+    <row r="824" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A824" s="2" t="s">
         <v>10</v>
       </c>
@@ -37344,7 +37352,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="825" spans="1:10">
+    <row r="825" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A825" s="2" t="s">
         <v>10</v>
       </c>
@@ -37376,7 +37384,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="826" spans="1:10">
+    <row r="826" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A826" s="2" t="s">
         <v>10</v>
       </c>
@@ -37408,7 +37416,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="827" spans="1:10">
+    <row r="827" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A827" s="2" t="s">
         <v>10</v>
       </c>
@@ -37440,7 +37448,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="828" spans="1:10">
+    <row r="828" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A828" s="2" t="s">
         <v>10</v>
       </c>
@@ -37472,7 +37480,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="829" spans="1:10">
+    <row r="829" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A829" s="2" t="s">
         <v>10</v>
       </c>
@@ -37504,7 +37512,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="830" spans="1:10">
+    <row r="830" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A830" s="2" t="s">
         <v>10</v>
       </c>
@@ -37536,7 +37544,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="831" spans="1:10">
+    <row r="831" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A831" s="2" t="s">
         <v>10</v>
       </c>
@@ -37568,7 +37576,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="832" spans="1:10">
+    <row r="832" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A832" s="2" t="s">
         <v>10</v>
       </c>
@@ -37600,7 +37608,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="833" spans="1:10">
+    <row r="833" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A833" s="2" t="s">
         <v>10</v>
       </c>
@@ -37632,7 +37640,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="834" spans="1:10">
+    <row r="834" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A834" s="2" t="s">
         <v>10</v>
       </c>
@@ -37664,7 +37672,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="835" spans="1:10">
+    <row r="835" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A835" s="2" t="s">
         <v>10</v>
       </c>
@@ -37696,7 +37704,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="836" spans="1:10">
+    <row r="836" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A836" s="2" t="s">
         <v>10</v>
       </c>
@@ -37728,7 +37736,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="837" spans="1:10">
+    <row r="837" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A837" s="2" t="s">
         <v>10</v>
       </c>
@@ -37760,7 +37768,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="838" spans="1:10">
+    <row r="838" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A838" s="2" t="s">
         <v>10</v>
       </c>
@@ -37792,7 +37800,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="839" spans="1:10">
+    <row r="839" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A839" s="2" t="s">
         <v>10</v>
       </c>
@@ -37824,7 +37832,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="840" spans="1:10">
+    <row r="840" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A840" s="2" t="s">
         <v>10</v>
       </c>
@@ -37856,7 +37864,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="841" spans="1:10">
+    <row r="841" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A841" s="2" t="s">
         <v>10</v>
       </c>
@@ -37888,7 +37896,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="842" spans="1:10">
+    <row r="842" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A842" s="2" t="s">
         <v>10</v>
       </c>
@@ -37920,7 +37928,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="843" spans="1:10">
+    <row r="843" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A843" s="2" t="s">
         <v>10</v>
       </c>
@@ -37952,7 +37960,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="844" spans="1:10">
+    <row r="844" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A844" s="2" t="s">
         <v>10</v>
       </c>
@@ -37984,7 +37992,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="845" spans="1:10">
+    <row r="845" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A845" s="2" t="s">
         <v>10</v>
       </c>
@@ -38016,7 +38024,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="846" spans="1:10">
+    <row r="846" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A846" s="2" t="s">
         <v>10</v>
       </c>
@@ -38048,7 +38056,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="847" spans="1:10">
+    <row r="847" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A847" s="2" t="s">
         <v>10</v>
       </c>
@@ -38080,7 +38088,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="848" spans="1:10">
+    <row r="848" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A848" s="2" t="s">
         <v>10</v>
       </c>
@@ -38112,7 +38120,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="849" spans="1:10">
+    <row r="849" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A849" s="2" t="s">
         <v>10</v>
       </c>
@@ -38144,7 +38152,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="850" spans="1:10">
+    <row r="850" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A850" s="2" t="s">
         <v>10</v>
       </c>
@@ -38176,7 +38184,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="851" spans="1:10">
+    <row r="851" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A851" s="2" t="s">
         <v>10</v>
       </c>
@@ -38208,7 +38216,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="852" spans="1:10">
+    <row r="852" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A852" s="2" t="s">
         <v>10</v>
       </c>
@@ -38240,7 +38248,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="853" spans="1:10">
+    <row r="853" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A853" s="2" t="s">
         <v>10</v>
       </c>
@@ -38272,7 +38280,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="854" spans="1:10">
+    <row r="854" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A854" s="2" t="s">
         <v>10</v>
       </c>
@@ -38304,7 +38312,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="855" spans="1:10">
+    <row r="855" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A855" s="2" t="s">
         <v>10</v>
       </c>
@@ -38336,7 +38344,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="856" spans="1:10">
+    <row r="856" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A856" s="2" t="s">
         <v>10</v>
       </c>
@@ -38368,7 +38376,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="857" spans="1:10">
+    <row r="857" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A857" s="2" t="s">
         <v>10</v>
       </c>
@@ -38400,7 +38408,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="858" spans="1:10">
+    <row r="858" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A858" s="2" t="s">
         <v>10</v>
       </c>
@@ -38432,7 +38440,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="859" spans="1:10">
+    <row r="859" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A859" s="2" t="s">
         <v>10</v>
       </c>
@@ -38464,7 +38472,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="860" spans="1:10">
+    <row r="860" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A860" s="2" t="s">
         <v>10</v>
       </c>
@@ -38496,7 +38504,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="861" spans="1:10">
+    <row r="861" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A861" s="2" t="s">
         <v>10</v>
       </c>
@@ -38528,7 +38536,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="862" spans="1:10">
+    <row r="862" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A862" s="2" t="s">
         <v>10</v>
       </c>
@@ -38560,7 +38568,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="863" spans="1:10">
+    <row r="863" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A863" s="2" t="s">
         <v>10</v>
       </c>
@@ -38592,7 +38600,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="864" spans="1:10">
+    <row r="864" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A864" s="2" t="s">
         <v>10</v>
       </c>
@@ -38624,7 +38632,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="865" spans="1:10">
+    <row r="865" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A865" s="2" t="s">
         <v>10</v>
       </c>
@@ -38656,7 +38664,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="866" spans="1:10">
+    <row r="866" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A866" s="2" t="s">
         <v>10</v>
       </c>
@@ -38688,7 +38696,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="867" spans="1:10">
+    <row r="867" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A867" s="2" t="s">
         <v>10</v>
       </c>
@@ -38720,7 +38728,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="868" spans="1:10">
+    <row r="868" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A868" s="2" t="s">
         <v>10</v>
       </c>
@@ -38752,7 +38760,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="869" spans="1:10">
+    <row r="869" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A869" s="2" t="s">
         <v>10</v>
       </c>
@@ -38784,7 +38792,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="870" spans="1:10">
+    <row r="870" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A870" s="2" t="s">
         <v>10</v>
       </c>
@@ -38816,7 +38824,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="871" spans="1:10">
+    <row r="871" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A871" s="2" t="s">
         <v>10</v>
       </c>
@@ -38848,7 +38856,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="872" spans="1:10">
+    <row r="872" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A872" s="2" t="s">
         <v>10</v>
       </c>
@@ -38880,7 +38888,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="873" spans="1:10">
+    <row r="873" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A873" s="2" t="s">
         <v>10</v>
       </c>
@@ -38912,7 +38920,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="874" spans="1:10">
+    <row r="874" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A874" s="2" t="s">
         <v>10</v>
       </c>
@@ -38944,7 +38952,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="875" spans="1:10">
+    <row r="875" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A875" s="2" t="s">
         <v>10</v>
       </c>
@@ -38976,7 +38984,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="876" spans="1:10">
+    <row r="876" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A876" s="2" t="s">
         <v>10</v>
       </c>
@@ -39008,7 +39016,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="877" spans="1:10">
+    <row r="877" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A877" s="2" t="s">
         <v>10</v>
       </c>
@@ -39040,7 +39048,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="878" spans="1:10">
+    <row r="878" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A878" s="2" t="s">
         <v>10</v>
       </c>
@@ -39072,7 +39080,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="879" spans="1:10">
+    <row r="879" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A879" s="2" t="s">
         <v>10</v>
       </c>
@@ -39104,7 +39112,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="880" spans="1:10">
+    <row r="880" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A880" s="2" t="s">
         <v>10</v>
       </c>
@@ -39136,7 +39144,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="881" spans="1:10">
+    <row r="881" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A881" s="2" t="s">
         <v>10</v>
       </c>
@@ -39168,7 +39176,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="882" spans="1:10">
+    <row r="882" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A882" s="2" t="s">
         <v>10</v>
       </c>
@@ -39200,7 +39208,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="883" spans="1:10">
+    <row r="883" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A883" s="2" t="s">
         <v>10</v>
       </c>
@@ -39232,7 +39240,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="884" spans="1:10">
+    <row r="884" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A884" s="2" t="s">
         <v>10</v>
       </c>
@@ -39264,7 +39272,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="885" spans="1:10">
+    <row r="885" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A885" s="2" t="s">
         <v>10</v>
       </c>
@@ -39296,7 +39304,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="886" spans="1:10">
+    <row r="886" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A886" s="2" t="s">
         <v>10</v>
       </c>
@@ -39328,7 +39336,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="887" spans="1:10">
+    <row r="887" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A887" s="2" t="s">
         <v>10</v>
       </c>
@@ -39360,7 +39368,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="888" spans="1:10">
+    <row r="888" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A888" s="2" t="s">
         <v>10</v>
       </c>
@@ -39392,7 +39400,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="889" spans="1:10">
+    <row r="889" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A889" s="2" t="s">
         <v>10</v>
       </c>
@@ -39424,7 +39432,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="890" spans="1:10">
+    <row r="890" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A890" s="2" t="s">
         <v>10</v>
       </c>
@@ -39456,7 +39464,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="891" spans="1:10">
+    <row r="891" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A891" s="2" t="s">
         <v>10</v>
       </c>
@@ -39488,7 +39496,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="892" spans="1:10">
+    <row r="892" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A892" s="2" t="s">
         <v>10</v>
       </c>
@@ -39520,7 +39528,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="893" spans="1:10">
+    <row r="893" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A893" s="2" t="s">
         <v>10</v>
       </c>
@@ -39552,7 +39560,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="894" spans="1:10">
+    <row r="894" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A894" s="2" t="s">
         <v>10</v>
       </c>
@@ -39584,7 +39592,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="895" spans="1:10">
+    <row r="895" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A895" s="2" t="s">
         <v>10</v>
       </c>
@@ -39616,7 +39624,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="896" spans="1:10">
+    <row r="896" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A896" s="2" t="s">
         <v>10</v>
       </c>
@@ -39648,7 +39656,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="897" spans="1:10">
+    <row r="897" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A897" s="2" t="s">
         <v>10</v>
       </c>
@@ -39680,7 +39688,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="898" spans="1:10">
+    <row r="898" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A898" s="2" t="s">
         <v>10</v>
       </c>
@@ -39712,7 +39720,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="899" spans="1:10">
+    <row r="899" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A899" s="2" t="s">
         <v>10</v>
       </c>
@@ -39744,7 +39752,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="900" spans="1:10">
+    <row r="900" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A900" s="2" t="s">
         <v>10</v>
       </c>
@@ -39776,7 +39784,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="901" spans="1:10">
+    <row r="901" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A901" s="2" t="s">
         <v>10</v>
       </c>
@@ -39808,7 +39816,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="902" spans="1:10">
+    <row r="902" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A902" s="2" t="s">
         <v>10</v>
       </c>
@@ -39840,7 +39848,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="903" spans="1:10">
+    <row r="903" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A903" s="2" t="s">
         <v>10</v>
       </c>
@@ -39872,7 +39880,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="904" spans="1:10">
+    <row r="904" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A904" s="2" t="s">
         <v>10</v>
       </c>
@@ -39904,7 +39912,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="905" spans="1:10">
+    <row r="905" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A905" s="2" t="s">
         <v>10</v>
       </c>
@@ -39936,7 +39944,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="906" spans="1:10">
+    <row r="906" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A906" s="2" t="s">
         <v>10</v>
       </c>
@@ -39968,7 +39976,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="907" spans="1:10">
+    <row r="907" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A907" s="2" t="s">
         <v>10</v>
       </c>
@@ -40000,7 +40008,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="908" spans="1:10">
+    <row r="908" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A908" s="2" t="s">
         <v>10</v>
       </c>
@@ -40032,7 +40040,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="909" spans="1:10">
+    <row r="909" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A909" s="2" t="s">
         <v>10</v>
       </c>
@@ -40064,7 +40072,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="910" spans="1:10">
+    <row r="910" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A910" s="2" t="s">
         <v>10</v>
       </c>
@@ -40096,7 +40104,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="911" spans="1:10">
+    <row r="911" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A911" s="2" t="s">
         <v>10</v>
       </c>
@@ -40138,90 +40146,90 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A17"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="120" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" ht="18" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>3448</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>3449</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>3450</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>3451</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>3452</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>3453</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>3454</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>3455</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>3456</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
     </row>
-    <row r="11" spans="1:1">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>3457</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>3458</v>
       </c>
     </row>
-    <row r="13" spans="1:1">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>3459</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>3460</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>3461</v>
       </c>
     </row>
-    <row r="16" spans="1:1">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>3462</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>3463</v>
       </c>
@@ -40234,7 +40242,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -40248,7 +40256,7 @@
     <col min="10" max="10" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
